--- a/FNDE/Centro Oeste/Entrega/EPI UNIFORME/fnde_resultado_merge.xlsx
+++ b/FNDE/Centro Oeste/Entrega/EPI UNIFORME/fnde_resultado_merge.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FNDE_output" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FNDE_output'!$A$1:$P$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FNDE_output'!$A$1:$P$76</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -456,7 +456,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P68"/>
+  <dimension ref="A1:P76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -705,47 +705,55 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>46308</v>
+          <t>MS</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>LIVPRO LTDA</t>
+          <t>COMERCIAL DE REFRIGERACAO PANAN OESTE LTDA (Panan)</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>60.147.971/0001-90</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n"/>
+          <t>15.448.996/0001-70</t>
+        </is>
+      </c>
+      <c r="H4" s="5" t="inlineStr">
+        <is>
+          <t>https://www.panan.com.br/pecas-e-epi/avental-e-camiseta/camiseta-profissional-branca-gg-para-cozinha-e-trabalho-em-poliester</t>
+        </is>
+      </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>Camiseta Masculina Malha PV Gola Redonda</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="n"/>
+          <t>Camiseta Profissional Branca GG para Cozinha e Trabalho em Poliéster.</t>
+        </is>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>53.5</v>
+      </c>
       <c r="K4" s="2" t="n"/>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>Malha PV aceita como malha fria (equivalência).</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="n"/>
-      <c r="N4" s="2" t="n"/>
+          <t>Característica não confirmada na página do produto: malha fria.</t>
+        </is>
+      </c>
+      <c r="M4" s="6" t="n">
+        <v>53.5</v>
+      </c>
+      <c r="N4" s="6" t="n">
+        <v>73.09</v>
+      </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="inlineStr">
-        <is>
-          <t>https://livpro.com.br/products/camiseta-masculina-malha-pv-gola-redonda?Cor=Azul-marinho&amp;Desenho+do+tecido=Lisa&amp;Tamanho=P</t>
-        </is>
-      </c>
+          <t>Opção mais barata para o CEP 74933-130: Correios Econômico R$ 73,09 7 a 9 dias úteis</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -765,7 +773,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
@@ -773,19 +781,27 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>A MASTER ARTIGOS PARA PROTECAO INDIVIDUAL E INDUSTRIAL LTDA (A Master EPI)</t>
+          <t>LIVPRO LTDA</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16.603.654/0001-40</t>
+          <t>60.147.971/0001-90</t>
         </is>
       </c>
       <c r="H5" s="2" t="n"/>
-      <c r="I5" s="3" t="n"/>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t>Camiseta Masculina Malha PV Gola Redonda</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="n"/>
       <c r="K5" s="2" t="n"/>
-      <c r="L5" s="2" t="n"/>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>Malha PV aceita como malha fria (equivalência).</t>
+        </is>
+      </c>
       <c r="M5" s="2" t="n"/>
       <c r="N5" s="2" t="n"/>
       <c r="O5" s="3" t="inlineStr">
@@ -795,7 +811,7 @@
       </c>
       <c r="P5" s="5" t="inlineStr">
         <is>
-          <t>https://www.amasterepi.com.br/busca?q=Camiseta%20De%20Uniforme</t>
+          <t>https://livpro.com.br/products/camiseta-masculina-malha-pv-gola-redonda?Cor=Azul-marinho&amp;Desenho+do+tecido=Lisa&amp;Tamanho=P</t>
         </is>
       </c>
     </row>
@@ -807,17 +823,17 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>1105</t>
+          <t>1104</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>CALÇA DE UNIFORME - TECIDO RESISTENTE (BRIM OU EQUIVALENTE), BOLSOS E FECHAMENTO FRONTAL.</t>
+          <t>CAMISETA/CAMISA DE UNIFORME - MALHA FRIA, GOLA REDONDA/ESPORTE, IDENTIFICAÇÃO DA EMPRESA; DEFINIR MANGA CURTA/LONGA CONFORME POSTO.</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
@@ -825,45 +841,31 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>SEGURANCA TOTAL EPIS LTDA</t>
+          <t>A MASTER ARTIGOS PARA PROTECAO INDIVIDUAL E INDUSTRIAL LTDA (A Master EPI)</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>39.268.527/0001-37</t>
-        </is>
-      </c>
-      <c r="H6" s="5" t="inlineStr">
-        <is>
-          <t>https://www.segurancatotal.com.br/calca-brim-azul</t>
-        </is>
-      </c>
-      <c r="I6" s="3" t="inlineStr">
-        <is>
-          <t>CALCA BRIM AZUL (Tamanho: 36)</t>
-        </is>
-      </c>
-      <c r="J6" s="6" t="n">
-        <v>59.37</v>
-      </c>
+          <t>16.603.654/0001-40</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n"/>
+      <c r="I6" s="3" t="n"/>
+      <c r="J6" s="2" t="n"/>
       <c r="K6" s="2" t="n"/>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: fechamento frontal.</t>
-        </is>
-      </c>
-      <c r="M6" s="6" t="n">
-        <v>59.37</v>
-      </c>
-      <c r="N6" s="6" t="n">
-        <v>20.44</v>
-      </c>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 20,44 7 dias úteis PAC R$ 30,06 3 dias úteis SEDEX</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="inlineStr">
+        <is>
+          <t>https://www.amasterepi.com.br/busca?q=Camiseta%20De%20Uniforme</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -891,26 +893,26 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20.838.307/0001-73</t>
+          <t>39.268.527/0001-37</t>
         </is>
       </c>
       <c r="H7" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojadoepi.com.br/calca-brim-profissional-elastico-total-preta-pr-22257-cal-ett-pt-4b-p5342?pp=/40.1488/</t>
+          <t>https://www.segurancatotal.com.br/calca-brim-azul</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>Calca Brim Profissional Elastico Total Preta</t>
+          <t>CALCA BRIM AZUL (Tamanho: 36)</t>
         </is>
       </c>
       <c r="J7" s="6" t="n">
-        <v>60.76</v>
+        <v>59.37</v>
       </c>
       <c r="K7" s="2" t="n"/>
       <c r="L7" s="2" t="inlineStr">
@@ -919,14 +921,14 @@
         </is>
       </c>
       <c r="M7" s="6" t="n">
-        <v>60.76</v>
+        <v>59.37</v>
       </c>
       <c r="N7" s="6" t="n">
-        <v>25.47</v>
+        <v>20.44</v>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Pac R$ 25,47 7 dia(s) útil(eis)</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,44 7 dias úteis PAC R$ 30,06 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P7" s="2" t="n"/>
@@ -949,34 +951,34 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>Multiseg Comercio de Equipamentos de Seguranca Ltda</t>
+          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>10.498.304/0001-84</t>
+          <t>20.838.307/0001-73</t>
         </is>
       </c>
       <c r="H8" s="5" t="inlineStr">
         <is>
-          <t>https://www.multiseg.com.br/752/cala-de-brim-branca-c-bolsos-profissional</t>
+          <t>https://www.lojadoepi.com.br/calca-brim-profissional-elastico-total-preta-pr-22257-cal-ett-pt-4b-p5342?pp=/40.1488/</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>Calça de Brim Branca Profissional com Bolsos Uniforme Operacional</t>
+          <t>Calca Brim Profissional Elastico Total Preta</t>
         </is>
       </c>
       <c r="J8" s="6" t="n">
-        <v>83.09999999999999</v>
+        <v>60.76</v>
       </c>
       <c r="K8" s="2" t="n"/>
       <c r="L8" s="2" t="inlineStr">
@@ -985,14 +987,14 @@
         </is>
       </c>
       <c r="M8" s="6" t="n">
-        <v>83.09999999999999</v>
+        <v>60.76</v>
       </c>
       <c r="N8" s="6" t="n">
-        <v>32.85</v>
+        <v>25.47</v>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Pac R$ 32,85 De 9 A 10 dia(s) Úteis</t>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 25,47 7 dia(s) útil(eis)</t>
         </is>
       </c>
       <c r="P8" s="2" t="n"/>
@@ -1015,43 +1017,53 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>LIVPRO LTDA</t>
+          <t>Multiseg Comercio de Equipamentos de Seguranca Ltda</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>60.147.971/0001-90</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n"/>
+          <t>10.498.304/0001-84</t>
+        </is>
+      </c>
+      <c r="H9" s="5" t="inlineStr">
+        <is>
+          <t>https://www.multiseg.com.br/752/cala-de-brim-branca-c-bolsos-profissional</t>
+        </is>
+      </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>Calça Operacional Refletiva com Elástico para Uniforme Operacional</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="n"/>
+          <t>Calça de Brim Branca Profissional com Bolsos Uniforme Operacional</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>83.09999999999999</v>
+      </c>
       <c r="K9" s="2" t="n"/>
-      <c r="L9" s="2" t="n"/>
-      <c r="M9" s="2" t="n"/>
-      <c r="N9" s="2" t="n"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: fechamento frontal.</t>
+        </is>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>83.09999999999999</v>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>32.85</v>
+      </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="inlineStr">
-        <is>
-          <t>https://livpro.com.br/products/calca-operacional-faixa-refletiva-poliester?Cor=Azul-royal&amp;Tamanho=M</t>
-        </is>
-      </c>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 32,85 De 9 A 10 dia(s) Úteis</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1071,7 +1083,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -1079,16 +1091,20 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>A MASTER ARTIGOS PARA PROTECAO INDIVIDUAL E INDUSTRIAL LTDA (A Master EPI)</t>
+          <t>LIVPRO LTDA</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>16.603.654/0001-40</t>
+          <t>60.147.971/0001-90</t>
         </is>
       </c>
       <c r="H10" s="2" t="n"/>
-      <c r="I10" s="3" t="n"/>
+      <c r="I10" s="3" t="inlineStr">
+        <is>
+          <t>Calça Operacional Refletiva com Elástico para Uniforme Operacional</t>
+        </is>
+      </c>
       <c r="J10" s="2" t="n"/>
       <c r="K10" s="2" t="n"/>
       <c r="L10" s="2" t="n"/>
@@ -1101,7 +1117,7 @@
       </c>
       <c r="P10" s="5" t="inlineStr">
         <is>
-          <t>https://www.amasterepi.com.br/busca?q=Cal%C3%A7a%20De%20Uniforme</t>
+          <t>https://livpro.com.br/products/calca-operacional-faixa-refletiva-poliester?Cor=Azul-royal&amp;Tamanho=M</t>
         </is>
       </c>
     </row>
@@ -1113,59 +1129,49 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>1107</t>
+          <t>1105</t>
         </is>
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t>CALÇADO DE SEGURANÇA ANTIDERRAPANTE - PROTEÇÃO CONTRA AGENTES MECÂNICOS; IMPERMEÁVEL QUANDO APLICÁVEL.</t>
+          <t>CALÇA DE UNIFORME - TECIDO RESISTENTE (BRIM OU EQUIVALENTE), BOLSOS E FECHAMENTO FRONTAL.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Multiseg Comercio de Equipamentos de Seguranca Ltda</t>
+          <t>A MASTER ARTIGOS PARA PROTECAO INDIVIDUAL E INDUSTRIAL LTDA (A Master EPI)</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10.498.304/0001-84</t>
-        </is>
-      </c>
-      <c r="H11" s="5" t="inlineStr">
-        <is>
-          <t>https://www.multiseg.com.br/4458/tenis-de-segurana-antiderrapante-sticky-shoe-copa-branco-ca-44589</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t>Tênis de Segurança Sticky Shoe Copa Branco Ca 44589 Antiderrapante</t>
-        </is>
-      </c>
-      <c r="J11" s="6" t="n">
-        <v>89.59999999999999</v>
-      </c>
+          <t>16.603.654/0001-40</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="3" t="n"/>
+      <c r="J11" s="2" t="n"/>
       <c r="K11" s="2" t="n"/>
       <c r="L11" s="2" t="n"/>
-      <c r="M11" s="6" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="N11" s="6" t="n">
-        <v>32.85</v>
-      </c>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Pac R$ 32,85 De 9 A 10 dia(s) Úteis</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P11" s="5" t="inlineStr">
+        <is>
+          <t>https://www.amasterepi.com.br/busca?q=Cal%C3%A7a%20De%20Uniforme</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1185,39 +1191,49 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>A MASTER ARTIGOS PARA PROTECAO INDIVIDUAL E INDUSTRIAL LTDA (A Master EPI)</t>
+          <t>Multiseg Comercio de Equipamentos de Seguranca Ltda</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>16.603.654/0001-40</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="n"/>
-      <c r="I12" s="3" t="n"/>
-      <c r="J12" s="2" t="n"/>
+          <t>10.498.304/0001-84</t>
+        </is>
+      </c>
+      <c r="H12" s="5" t="inlineStr">
+        <is>
+          <t>https://www.multiseg.com.br/4458/tenis-de-segurana-antiderrapante-sticky-shoe-copa-branco-ca-44589</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t>Tênis de Segurança Sticky Shoe Copa Branco Ca 44589 Antiderrapante</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>89.59999999999999</v>
+      </c>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
-      <c r="M12" s="2" t="n"/>
-      <c r="N12" s="2" t="n"/>
+      <c r="M12" s="6" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>32.85</v>
+      </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
-        </is>
-      </c>
-      <c r="P12" s="5" t="inlineStr">
-        <is>
-          <t>https://www.amasterepi.com.br/busca?q=Cal%C3%A7ado%20De%20Seguran%C3%A7a%20Antiderrapante</t>
-        </is>
-      </c>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 32,85 De 9 A 10 dia(s) Úteis</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1227,17 +1243,17 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t>BOTA DE PVC/BORRACHA - IMPERMEÁVEL, SOLADO ANTIDERRAPANTE, CANO MÉDIO OU LONGO.</t>
+          <t>CALÇADO DE SEGURANÇA ANTIDERRAPANTE - PROTEÇÃO CONTRA AGENTES MECÂNICOS; IMPERMEÁVEL QUANDO APLICÁVEL.</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
@@ -1245,45 +1261,31 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+          <t>A MASTER ARTIGOS PARA PROTECAO INDIVIDUAL E INDUSTRIAL LTDA (A Master EPI)</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>27.061.442/0002-85</t>
-        </is>
-      </c>
-      <c r="H13" s="5" t="inlineStr">
-        <is>
-          <t>https://www.lojas360.com.br/bicodepvc/bota-de-pvc-cano-longo-preta-com-forro-biqueira-composite?variant_id=5711</t>
-        </is>
-      </c>
-      <c r="I13" s="3" t="inlineStr">
-        <is>
-          <t>Bota de Pvc Cano Longo Preta Com Forro Biqueira Composite</t>
-        </is>
-      </c>
-      <c r="J13" s="6" t="n">
-        <v>176.61</v>
-      </c>
+          <t>16.603.654/0001-40</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="3" t="n"/>
+      <c r="J13" s="2" t="n"/>
       <c r="K13" s="2" t="n"/>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>PVC aceito como impermeável (equivalência).</t>
-        </is>
-      </c>
-      <c r="M13" s="6" t="n">
-        <v>176.61</v>
-      </c>
-      <c r="N13" s="6" t="n">
-        <v>1687.82</v>
-      </c>
+      <c r="L13" s="2" t="n"/>
+      <c r="M13" s="2" t="n"/>
+      <c r="N13" s="2" t="n"/>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Frete Valor Prazo de Entrega e Observações: Logística Própria FAVORITA R$ 1.687,82 Até 5 a 6 dia(s) úteis após o faturamento do pedido FRETE GRÁTIS PA</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.amasterepi.com.br/busca?q=Cal%C3%A7ado%20De%20Seguran%C3%A7a%20Antiderrapante</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1311,42 +1313,42 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>SEGURANCA TOTAL EPIS LTDA</t>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>39.268.527/0001-37</t>
+          <t>27.061.442/0002-85</t>
         </is>
       </c>
       <c r="H14" s="5" t="inlineStr">
         <is>
-          <t>https://www.segurancatotal.com.br/bota-pvc-impermeavel-branco</t>
+          <t>https://www.lojas360.com.br/bicodepvc/bota-de-pvc-cano-longo-preta-com-forro-biqueira-composite?variant_id=5711</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t>Bota PVC Impermeável Innpro Cano Médio Branco CA 36025 (numeração innpro: 34/35)</t>
+          <t>Bota de Pvc Cano Longo Preta Com Forro Biqueira Composite</t>
         </is>
       </c>
       <c r="J14" s="6" t="n">
-        <v>55.05</v>
+        <v>176.61</v>
       </c>
       <c r="K14" s="2" t="n"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: solado antiderrapante.</t>
+          <t>PVC aceito como impermeável (equivalência).</t>
         </is>
       </c>
       <c r="M14" s="6" t="n">
-        <v>55.05</v>
+        <v>176.61</v>
       </c>
       <c r="N14" s="6" t="n">
-        <v>18.4</v>
+        <v>1687.82</v>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
+          <t>Opção mais barata para o CEP 74933-130: Frete Valor Prazo de Entrega e Observações: Logística Própria FAVORITA R$ 1.687,82 Até 5 a 6 dia(s) úteis após o faturamento do pedido FRETE GRÁTIS PA</t>
         </is>
       </c>
       <c r="P14" s="2" t="n"/>
@@ -1369,7 +1371,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
@@ -1377,40 +1379,42 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Casa do Pica-Pau Ltda</t>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>50.223.823/0001-54</t>
+          <t>39.268.527/0001-37</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>https://www.casadopicapau.com.br/bota-galocha-baspan-ultraleve-pvc-cano-longo-azul-amarelo-nautica/p</t>
+          <t>https://www.segurancatotal.com.br/bota-pvc-impermeavel-branco</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Bota Galocha Baspan Ultraleve de PVC Cano Longo</t>
+          <t>Bota PVC Impermeável Innpro Cano Médio Branco CA 36025 (numeração innpro: 34/35)</t>
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>60.41</v>
+        <v>55.05</v>
       </c>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>PVC aceito como impermeável (equivalência).</t>
+          <t>Característica não confirmada na página do produto: solado antiderrapante.</t>
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>60.41</v>
-      </c>
-      <c r="N15" s="2" t="n"/>
+        <v>55.05</v>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>18.4</v>
+      </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO) | frete real: R$ 18,70</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P15" s="2" t="n"/>
@@ -1433,7 +1437,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -1441,26 +1445,26 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
+          <t>Casa do Pica-Pau Ltda</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>20.838.307/0001-73</t>
+          <t>50.223.823/0001-54</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojadoepi.com.br/bota-de-pvc-work-cano-medio-cor-preta-comprimento-28-cm-ca-36025-innpro-p3301?pp=/40.1438/</t>
+          <t>https://www.casadopicapau.com.br/bota-galocha-baspan-ultraleve-pvc-cano-longo-azul-amarelo-nautica/p</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Bota de PVC Work Cano Médio Cor Preta Comprimento 28 cm CA 36025 INNPRO</t>
+          <t>Bota Galocha Baspan Ultraleve de PVC Cano Longo</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>44.56</v>
+        <v>60.41</v>
       </c>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="inlineStr">
@@ -1469,14 +1473,12 @@
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>44.56</v>
-      </c>
-      <c r="N16" s="6" t="n">
-        <v>25.47</v>
-      </c>
+        <v>60.41</v>
+      </c>
+      <c r="N16" s="2" t="n"/>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Pac R$ 25,47 7 dia(s) útil(eis)</t>
+          <t>Frete não calculado (GO para GO) | frete real: R$ 18,70</t>
         </is>
       </c>
       <c r="P16" s="2" t="n"/>
@@ -1499,50 +1501,50 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Panan</t>
+          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15.448.996/0001-70</t>
+          <t>20.838.307/0001-73</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>https://www.panan.com.br/pecas-e-epis/calcados/bota-pvc-cano-longo-n-41-bpcl11-vulcabras</t>
+          <t>https://www.lojadoepi.com.br/bota-de-pvc-work-cano-medio-cor-preta-comprimento-28-cm-ca-36025-innpro-p3301?pp=/40.1438/</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Bota PVC Cano Longo N° 41 BPCL11 - Vulcabras</t>
+          <t>Bota de PVC Work Cano Médio Cor Preta Comprimento 28 cm CA 36025 INNPRO</t>
         </is>
       </c>
       <c r="J17" s="6" t="n">
-        <v>86.90000000000001</v>
+        <v>44.56</v>
       </c>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>PVC aceito como impermeável (equivalência). Característica não confirmada na página do produto: solado antiderrapante.</t>
+          <t>PVC aceito como impermeável (equivalência).</t>
         </is>
       </c>
       <c r="M17" s="6" t="n">
-        <v>86.90000000000001</v>
+        <v>44.56</v>
       </c>
       <c r="N17" s="6" t="n">
-        <v>38.7</v>
+        <v>25.47</v>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Correios Econômico R$ 38,70 7 a 9 dias úteis</t>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 25,47 7 dia(s) útil(eis)</t>
         </is>
       </c>
       <c r="P17" s="2" t="n"/>
@@ -1555,56 +1557,60 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t>LUVA DE PVC - CANO MÉDIO OU LONGO; PARA ATIVIDADES DE LIMPEZA.</t>
+          <t>BOTA DE PVC/BORRACHA - IMPERMEÁVEL, SOLADO ANTIDERRAPANTE, CANO MÉDIO OU LONGO.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+          <t>Panan</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>27.061.442/0002-85</t>
+          <t>15.448.996/0001-70</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojas360.com.br/luvas-de-seguranca/luva-de-pvc-sem-forro-palma-aspera-70cm-com-ombreira</t>
+          <t>https://www.panan.com.br/pecas-e-epis/calcados/bota-pvc-cano-longo-n-41-bpcl11-vulcabras</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Luva de PVC Sem Forro Palma Áspera 70cm Com Ombreira</t>
+          <t>Bota PVC Cano Longo N° 41 BPCL11 - Vulcabras</t>
         </is>
       </c>
       <c r="J18" s="6" t="n">
-        <v>52.44</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K18" s="2" t="n"/>
-      <c r="L18" s="2" t="n"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>PVC aceito como impermeável (equivalência). Característica não confirmada na página do produto: solado antiderrapante.</t>
+        </is>
+      </c>
       <c r="M18" s="6" t="n">
-        <v>52.44</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>18.4</v>
+        <v>38.7</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
+          <t>Opção mais barata para o CEP 74933-130: Correios Econômico R$ 38,70 7 a 9 dias úteis</t>
         </is>
       </c>
       <c r="P18" s="2" t="n"/>
@@ -1635,38 +1641,38 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>20.838.307/0001-73</t>
+          <t>27.061.442/0002-85</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojadoepi.com.br/luva-de-pvc-para-jatista-ca-43248-ldi-safety-107-p2283</t>
+          <t>https://www.lojas360.com.br/luvas-de-seguranca/luva-de-pvc-sem-forro-palma-aspera-70cm-com-ombreira</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Luva de PVC para Jatista CA 43248 LDI Safety</t>
+          <t>Luva de PVC Sem Forro Palma Áspera 70cm Com Ombreira</t>
         </is>
       </c>
       <c r="J19" s="6" t="n">
-        <v>65.88</v>
+        <v>52.44</v>
       </c>
       <c r="K19" s="2" t="n"/>
       <c r="L19" s="2" t="n"/>
       <c r="M19" s="6" t="n">
-        <v>65.88</v>
+        <v>52.44</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>27.98</v>
+        <v>18.4</v>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Pac R$ 27,98 7 dia(s) útil(eis)</t>
+          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
         </is>
       </c>
       <c r="P19" s="2" t="n"/>
@@ -1689,44 +1695,46 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E20" s="4" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Goiás Ferramentas</t>
+          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>09.497.806/0001-01</t>
+          <t>20.838.307/0001-73</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>https://www.goiasferramentas.com.br/produto/615-luva-de-pvc-cano-longo-45cm-kalipso</t>
+          <t>https://www.lojadoepi.com.br/luva-de-pvc-para-jatista-ca-43248-ldi-safety-107-p2283</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Luva de PVC Cano Longo 45cm Kalipso</t>
+          <t>Luva de PVC para Jatista CA 43248 LDI Safety</t>
         </is>
       </c>
       <c r="J20" s="6" t="n">
-        <v>23.33</v>
+        <v>65.88</v>
       </c>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="6" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="N20" s="2" t="n"/>
+        <v>65.88</v>
+      </c>
+      <c r="N20" s="6" t="n">
+        <v>27.98</v>
+      </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO)</t>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 27,98 7 dia(s) útil(eis)</t>
         </is>
       </c>
       <c r="P20" s="2" t="n"/>
@@ -1753,35 +1761,35 @@
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Fermarcs Ferramentas</t>
+          <t>Goiás Ferramentas</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>08.615.223/0001-75</t>
+          <t>09.497.806/0001-01</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>https://www.fermarcsferramentas.com.br/luvas/luva-pvc-azul-s-forro-palma-lisa-35cm-ca34593</t>
+          <t>https://www.goiasferramentas.com.br/produto/615-luva-de-pvc-cano-longo-45cm-kalipso</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Luva Pvc Azul S/ Forro Palma Lisa 35cm Ca34593</t>
+          <t>Luva de PVC Cano Longo 45cm Kalipso</t>
         </is>
       </c>
       <c r="J21" s="6" t="n">
-        <v>24.9</v>
+        <v>23.33</v>
       </c>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="6" t="n">
-        <v>24.9</v>
+        <v>23.33</v>
       </c>
       <c r="N21" s="2" t="n"/>
       <c r="O21" s="3" t="inlineStr">
@@ -1799,60 +1807,54 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t>LUVA DE LÁTEX FORRADA - CANO CURTO; TAMANHOS VARIADOS.</t>
+          <t>LUVA DE PVC - CANO MÉDIO OU LONGO; PARA ATIVIDADES DE LIMPEZA.</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
+          <t>Fermarcs Ferramentas</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>31.893.116/0001-20</t>
+          <t>08.615.223/0001-75</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>https://www.loja.bhzepi.com.br/luva-latex-amarela-forrada-ca-42023-imbat</t>
+          <t>https://www.fermarcsferramentas.com.br/luvas/luva-pvc-azul-s-forro-palma-lisa-35cm-ca34593</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>LUVA LATEX AMARELA FORRADA CA 42023 IMBAT (Tamanho: M)</t>
+          <t>Luva Pvc Azul S/ Forro Palma Lisa 35cm Ca34593</t>
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>5</v>
+        <v>24.9</v>
       </c>
       <c r="K22" s="2" t="n"/>
-      <c r="L22" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: cano curto.</t>
-        </is>
-      </c>
+      <c r="L22" s="2" t="n"/>
       <c r="M22" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N22" s="6" t="n">
-        <v>20.62</v>
-      </c>
+        <v>24.9</v>
+      </c>
+      <c r="N22" s="2" t="n"/>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC R$ 26,55 5 dias úteis Jadlog Package R$ 40,39 3 dias úteis SEDEX</t>
+          <t>Frete não calculado (GO para GO)</t>
         </is>
       </c>
       <c r="P22" s="2" t="n"/>
@@ -1875,7 +1877,7 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
@@ -1883,42 +1885,42 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>27.061.442/0002-85</t>
+          <t>31.893.116/0001-20</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojas360.com.br/luvas-de-seguranca/luva-latex-antiderrapante-orange-kalipso-c-a-32499?variant_id=4253</t>
+          <t>https://www.loja.bhzepi.com.br/luva-latex-amarela-forrada-ca-42023-imbat</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>Luva Látex Antiderrapante Orange Kalipso | C.A. 32499</t>
+          <t>LUVA LATEX AMARELA FORRADA CA 42023 IMBAT (Tamanho: M)</t>
         </is>
       </c>
       <c r="J23" s="6" t="n">
-        <v>12.26</v>
+        <v>5</v>
       </c>
       <c r="K23" s="2" t="n"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: forrada, cano curto.</t>
+          <t>Característica não confirmada na página do produto: cano curto.</t>
         </is>
       </c>
       <c r="M23" s="6" t="n">
-        <v>12.26</v>
+        <v>5</v>
       </c>
       <c r="N23" s="6" t="n">
-        <v>18.4</v>
+        <v>20.62</v>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC R$ 26,55 5 dias úteis Jadlog Package R$ 40,39 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P23" s="2" t="n"/>
@@ -1941,7 +1943,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -1949,42 +1951,42 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
+          <t>27.061.442/0002-85</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>https://www.supriflex.com.br/produto/luva-latex-multiuso-quality-forte-vabene-verde-p.html</t>
+          <t>https://www.lojas360.com.br/luvas-de-seguranca/luva-latex-antiderrapante-orange-kalipso-c-a-32499?variant_id=4253</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Luva Látex Multiuso Quality Forte Vabene Verde P</t>
+          <t>Luva Látex Antiderrapante Orange Kalipso | C.A. 32499</t>
         </is>
       </c>
       <c r="J24" s="6" t="n">
-        <v>4.99</v>
+        <v>12.26</v>
       </c>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: cano curto.</t>
+          <t>Característica não confirmada na página do produto: forrada, cano curto.</t>
         </is>
       </c>
       <c r="M24" s="6" t="n">
-        <v>4.99</v>
+        <v>12.26</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>28.06</v>
+        <v>18.4</v>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 28,06 11 dias úteis Correios - Mini Envios R$ 31,54 7 dias úteis Correios PAC R$ 32,18 7 dias úteis Jadlog - .Package</t>
+          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
         </is>
       </c>
       <c r="P24" s="2" t="n"/>
@@ -2007,34 +2009,34 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>Multiseg Comercio de Equipamentos de Seguranca Ltda</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>10.498.304/0001-84</t>
+          <t>46.412.993/0001-00</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>https://www.multiseg.com.br/1619/luva-ltex-neoprene-supermix-super-safety</t>
+          <t>https://www.supriflex.com.br/produto/luva-latex-multiuso-quality-forte-vabene-verde-p.html</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Luva de Látex e Neoprene Super MIX Forrada Super Safety Bicolor - Ca 33333</t>
+          <t>Luva Látex Multiuso Quality Forte Vabene Verde P</t>
         </is>
       </c>
       <c r="J25" s="6" t="n">
-        <v>9.98</v>
+        <v>4.99</v>
       </c>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="inlineStr">
@@ -2043,14 +2045,14 @@
         </is>
       </c>
       <c r="M25" s="6" t="n">
-        <v>9.98</v>
+        <v>4.99</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>32.85</v>
+        <v>28.06</v>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Pac R$ 32,85 De 9 A 10 dia(s) Úteis</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 28,06 11 dias úteis Correios - Mini Envios R$ 31,54 7 dias úteis Correios PAC R$ 32,18 7 dias úteis Jadlog - .Package</t>
         </is>
       </c>
       <c r="P25" s="2" t="n"/>
@@ -2063,56 +2065,62 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>LUVA DE NEOPRENE - TAMANHOS VARIADOS; PARA MANIPULAÇÃO COMPATÍVEL DE PRODUTOS QUÍMICOS.</t>
+          <t>LUVA DE LÁTEX FORRADA - CANO CURTO; TAMANHOS VARIADOS.</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>46308</v>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>31.893.116/0001-20</t>
+          <t>39.268.527/0001-37</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>https://www.loja.bhzepi.com.br/luva-latex-neoprene-bicolor-ca16779-volk</t>
+          <t>https://www.segurancatotal.com.br/luva-de-latex-kalipso-amarela-ca-13959</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>LUVA LATEX NEOPRENE BICOLOR CA16779 VOLK (Tamanho: M)</t>
+          <t>Luva de Látex Multiuso Kalipso Amarela CA13959 (Tamanho: P)</t>
         </is>
       </c>
       <c r="J26" s="6" t="n">
-        <v>13</v>
+        <v>4.69</v>
       </c>
       <c r="K26" s="2" t="n"/>
-      <c r="L26" s="2" t="n"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: cano curto.</t>
+        </is>
+      </c>
       <c r="M26" s="6" t="n">
-        <v>13</v>
+        <v>4.69</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>20.62</v>
+        <v>18.4</v>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC R$ 26,55 5 dias úteis Jadlog Package R$ 40,39 3 dias úteis SEDEX</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC</t>
         </is>
       </c>
       <c r="P26" s="2" t="n"/>
@@ -2125,56 +2133,60 @@
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t>LUVA DE NEOPRENE - TAMANHOS VARIADOS; PARA MANIPULAÇÃO COMPATÍVEL DE PRODUTOS QUÍMICOS.</t>
+          <t>LUVA DE LÁTEX FORRADA - CANO CURTO; TAMANHOS VARIADOS.</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E27" s="4" t="n">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+          <t>Multiseg Comercio de Equipamentos de Seguranca Ltda</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>27.061.442/0002-85</t>
+          <t>10.498.304/0001-84</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojas360.com.br/protecao-das-maos/luva-latex-neoprene-amareloazul-pl-7004-plastcor-c-a-43916?variant_id=5131</t>
+          <t>https://www.multiseg.com.br/1619/luva-ltex-neoprene-supermix-super-safety</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Luva Látex Neoprene Amarelo/Azul Pl 7004 Plastcor | C.A. 43916</t>
+          <t>Luva de Látex e Neoprene Super MIX Forrada Super Safety Bicolor - Ca 33333</t>
         </is>
       </c>
       <c r="J27" s="6" t="n">
-        <v>9.31</v>
+        <v>9.98</v>
       </c>
       <c r="K27" s="2" t="n"/>
-      <c r="L27" s="2" t="n"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: cano curto.</t>
+        </is>
+      </c>
       <c r="M27" s="6" t="n">
-        <v>9.31</v>
+        <v>9.98</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>18.4</v>
+        <v>32.85</v>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 32,85 De 9 A 10 dia(s) Úteis</t>
         </is>
       </c>
       <c r="P27" s="2" t="n"/>
@@ -2197,7 +2209,7 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
@@ -2205,38 +2217,38 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>SEGURANCA TOTAL EPIS LTDA</t>
+          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>39.268.527/0001-37</t>
+          <t>31.893.116/0001-20</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>https://www.segurancatotal.com.br/luva-latexneoprene-supermix-super-safety-ca-33333</t>
+          <t>https://www.loja.bhzepi.com.br/luva-latex-neoprene-bicolor-ca16779-volk</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>Luva Látex/Neoprene Supermix Super Safety CA 33333 (Tamanho das Luvas: 7/P)</t>
+          <t>LUVA LATEX NEOPRENE BICOLOR CA16779 VOLK (Tamanho: M)</t>
         </is>
       </c>
       <c r="J28" s="6" t="n">
-        <v>10.41</v>
+        <v>13</v>
       </c>
       <c r="K28" s="2" t="n"/>
       <c r="L28" s="2" t="n"/>
       <c r="M28" s="6" t="n">
-        <v>10.41</v>
+        <v>13</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>18.4</v>
+        <v>20.62</v>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC R$ 26,55 5 dias úteis Jadlog Package R$ 40,39 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P28" s="2" t="n"/>
@@ -2259,44 +2271,46 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>Goiás Ferramentas</t>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>09.497.806/0001-01</t>
+          <t>27.061.442/0002-85</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>https://www.goiasferramentas.com.br/produto/13963-luva-de-latex-neoprene-kalipso-neoprex-azul-e-amarela-xg</t>
+          <t>https://www.lojas360.com.br/protecao-das-maos/luva-latex-neoprene-amareloazul-pl-7004-plastcor-c-a-43916?variant_id=5131</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Luva de Latex / Neoprene Kalipso Neoprex Azul e Amarela XG</t>
+          <t>Luva Látex Neoprene Amarelo/Azul Pl 7004 Plastcor | C.A. 43916</t>
         </is>
       </c>
       <c r="J29" s="6" t="n">
-        <v>10.88</v>
+        <v>9.31</v>
       </c>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="6" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="N29" s="2" t="n"/>
+        <v>9.31</v>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>18.4</v>
+      </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO)</t>
+          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
         </is>
       </c>
       <c r="P29" s="2" t="n"/>
@@ -2319,46 +2333,46 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E30" s="4" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>A Master EPI</t>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>16.603.654/0001-40</t>
+          <t>39.268.527/0001-37</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>https://www.amasterepi.com.br/21946/luva-de-latex-neoprene-bicolor-std-volk-p</t>
+          <t>https://www.segurancatotal.com.br/luva-latexneoprene-supermix-super-safety-ca-33333</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Luva de Latex Neoprene Bicolor Std Volk</t>
+          <t>Luva Látex/Neoprene Supermix Super Safety CA 33333 (Tamanho das Luvas: 7/P)</t>
         </is>
       </c>
       <c r="J30" s="6" t="n">
-        <v>10.5</v>
+        <v>10.41</v>
       </c>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="6" t="n">
-        <v>10.5</v>
+        <v>10.41</v>
       </c>
       <c r="N30" s="6" t="n">
-        <v>32.85</v>
+        <v>18.4</v>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Entrega Econômica R$ 32,85 De 6 A 7 dia(s) Úteis</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P30" s="2" t="n"/>
@@ -2371,56 +2385,54 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>LUVA DE ALGODÃO PIGMENTADA - PARA ATIVIDADES DE APOIO/MANUSEIO.</t>
+          <t>LUVA DE NEOPRENE - TAMANHOS VARIADOS; PARA MANIPULAÇÃO COMPATÍVEL DE PRODUTOS QUÍMICOS.</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>SEGURANCA TOTAL EPIS LTDA</t>
+          <t>Goiás Ferramentas</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>39.268.527/0001-37</t>
+          <t>09.497.806/0001-01</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>https://www.segurancatotal.com.br/produto/luva-tricotada-pigmentada-preta-handex-4-fios.html</t>
+          <t>https://www.goiasferramentas.com.br/produto/13963-luva-de-latex-neoprene-kalipso-neoprex-azul-e-amarela-xg</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Luva Tricotada Pigmentada Preta Handex 4 Fios</t>
+          <t>Luva de Latex / Neoprene Kalipso Neoprex Azul e Amarela XG</t>
         </is>
       </c>
       <c r="J31" s="6" t="n">
-        <v>3.09</v>
+        <v>10.88</v>
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="6" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="N31" s="6" t="n">
-        <v>18.4</v>
-      </c>
+        <v>10.88</v>
+      </c>
+      <c r="N31" s="2" t="n"/>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
+          <t>Frete não calculado (GO para GO)</t>
         </is>
       </c>
       <c r="P31" s="2" t="n"/>
@@ -2433,12 +2445,12 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t>LUVA DE ALGODÃO PIGMENTADA - PARA ATIVIDADES DE APOIO/MANUSEIO.</t>
+          <t>LUVA DE NEOPRENE - TAMANHOS VARIADOS; PARA MANIPULAÇÃO COMPATÍVEL DE PRODUTOS QUÍMICOS.</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2451,38 +2463,38 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>TR Distribuidora</t>
+          <t>A Master EPI</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>14.213.841/0001-91</t>
+          <t>16.603.654/0001-40</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>https://www.trepis.com.br/luva-em-algodao-tricotada-modelo-cotton-black-sem-banho-e-com-pigmento-riscos-mecanicos-c-a-36347</t>
+          <t>https://www.amasterepi.com.br/21946/luva-de-latex-neoprene-bicolor-std-volk-p</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Luva de Algodão Tricotada Cotton Black Pigmentada para Riscos Mecânicos C.A. 36347</t>
+          <t>Luva de Latex Neoprene Bicolor Std Volk</t>
         </is>
       </c>
       <c r="J32" s="6" t="n">
-        <v>2.82</v>
+        <v>10.5</v>
       </c>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="6" t="n">
-        <v>2.82</v>
+        <v>10.5</v>
       </c>
       <c r="N32" s="6" t="n">
-        <v>21.55</v>
+        <v>32.85</v>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: JADLOG .Package R$ 21,55 Capital de todo Brasil: 01 a 03 dias. Interior de Todo Brasil: 02 a 05 dias.</t>
+          <t>Opção mais barata para o CEP 74933-130: Entrega Econômica R$ 32,85 De 6 A 7 dia(s) Úteis</t>
         </is>
       </c>
       <c r="P32" s="2" t="n"/>
@@ -2513,38 +2525,38 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>Dimensional Brasil Solucoes Ltda</t>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>06.913.480/0001-68</t>
+          <t>39.268.527/0001-37</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>https://www.dimensional.com.br/luva-algodaopoliester-preta-pigmentada-tamanho-9-tatex-021123-kalipso/p</t>
+          <t>https://www.segurancatotal.com.br/produto/luva-tricotada-pigmentada-preta-handex-4-fios.html</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Luva Algodao/Poliester Preta Pigmentada Tatex 02.11.2.3 Tamanho 9 Kalipso</t>
+          <t>Luva Tricotada Pigmentada Preta Handex 4 Fios</t>
         </is>
       </c>
       <c r="J33" s="6" t="n">
-        <v>2.09</v>
+        <v>3.09</v>
       </c>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
       <c r="M33" s="6" t="n">
-        <v>2.09</v>
+        <v>3.09</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>52.84</v>
+        <v>18.4</v>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Transportadora Em até 6 dias úteis R$ 52,84</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P33" s="2" t="n"/>
@@ -2557,56 +2569,56 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t>ÓCULOS DE PROTEÇÃO INCOLOR - PARA MANIPULAÇÃO E APLICAÇÃO DE PRODUTOS QUÍMICOS.</t>
+          <t>LUVA DE ALGODÃO PIGMENTADA - PARA ATIVIDADES DE APOIO/MANUSEIO.</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
+          <t>TR Distribuidora</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>31.893.116/0001-20</t>
+          <t>14.213.841/0001-91</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>https://www.loja.bhzepi.com.br/produto/oculos-de-seguranca-roma-incolor-protecao-uv-antirrisco</t>
+          <t>https://www.trepis.com.br/luva-em-algodao-tricotada-modelo-cotton-black-sem-banho-e-com-pigmento-riscos-mecanicos-c-a-36347</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Oculos De Segurança Roma Incolor Proteção Uv Antirrisco</t>
+          <t>Luva de Algodão Tricotada Cotton Black Pigmentada para Riscos Mecânicos C.A. 36347</t>
         </is>
       </c>
       <c r="J34" s="6" t="n">
-        <v>70</v>
+        <v>2.82</v>
       </c>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
       <c r="M34" s="6" t="n">
-        <v>70</v>
+        <v>2.82</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>20.62</v>
+        <v>21.55</v>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC R$ 26,55 5 dias úteis Jadlog Package R$ 40,39 3 dias úteis SEDEX</t>
+          <t>Opção mais barata para o CEP 74933-130: JADLOG .Package R$ 21,55 Capital de todo Brasil: 01 a 03 dias. Interior de Todo Brasil: 02 a 05 dias.</t>
         </is>
       </c>
       <c r="P34" s="2" t="n"/>
@@ -2619,56 +2631,58 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t>ÓCULOS DE PROTEÇÃO INCOLOR - PARA MANIPULAÇÃO E APLICAÇÃO DE PRODUTOS QUÍMICOS.</t>
+          <t>LUVA DE ALGODÃO PIGMENTADA - PARA ATIVIDADES DE APOIO/MANUSEIO.</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>46308</v>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>27.061.442/0002-85</t>
+          <t>31.893.116/0001-20</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojas360.com.br/oculos-de-seguranca-urano</t>
+          <t>https://www.loja.bhzepi.com.br/luva-de-segurana-malha-tricotada-pigmentada-branca</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Óculos de Segurança Urano Incolor Anti Risco | C.A. 42547</t>
+          <t>Luva De Segurança Malha Tricotada Pigmentada branca</t>
         </is>
       </c>
       <c r="J35" s="6" t="n">
-        <v>9.41</v>
+        <v>3.9</v>
       </c>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="6" t="n">
-        <v>9.41</v>
+        <v>3.9</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>18.4</v>
+        <v>20.62</v>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC</t>
         </is>
       </c>
       <c r="P35" s="2" t="n"/>
@@ -2681,12 +2695,12 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>ÓCULOS DE PROTEÇÃO INCOLOR - PARA MANIPULAÇÃO E APLICAÇÃO DE PRODUTOS QUÍMICOS.</t>
+          <t>LUVA DE ALGODÃO PIGMENTADA - PARA ATIVIDADES DE APOIO/MANUSEIO.</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2699,38 +2713,38 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>SEGURANCA TOTAL EPIS LTDA</t>
+          <t>Dimensional Brasil Solucoes Ltda</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>39.268.527/0001-37</t>
+          <t>06.913.480/0001-68</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>https://www.segurancatotal.com.br/produto/oculos-de-protecao-sky-deltaplus-incolor.html</t>
+          <t>https://www.dimensional.com.br/luva-algodaopoliester-preta-pigmentada-tamanho-9-tatex-021123-kalipso/p</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Óculos De Proteção Sky Deltaplus Incolor</t>
+          <t>Luva Algodao/Poliester Preta Pigmentada Tatex 02.11.2.3 Tamanho 9 Kalipso</t>
         </is>
       </c>
       <c r="J36" s="6" t="n">
-        <v>3.99</v>
+        <v>2.09</v>
       </c>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="6" t="n">
-        <v>3.99</v>
+        <v>2.09</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>18.4</v>
+        <v>52.84</v>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
+          <t>Opção mais barata para o CEP 74933-130: Transportadora Em até 6 dias úteis R$ 52,84</t>
         </is>
       </c>
       <c r="P36" s="2" t="n"/>
@@ -2753,7 +2767,7 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
@@ -2761,36 +2775,38 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>ZEUS DO BRASIL LTDA (loja EPI Zeus)</t>
+          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>82.699.588/0001-88</t>
+          <t>31.893.116/0001-20</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>https://www.epizeus.com.br/oculos-protec-o-lente-incolor-policarbonato-ca-28018</t>
+          <t>https://www.loja.bhzepi.com.br/produto/oculos-de-seguranca-roma-incolor-protecao-uv-antirrisco</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Óculos proteção lente incolor policarbonato - CA 10346</t>
+          <t>Oculos De Segurança Roma Incolor Proteção Uv Antirrisco</t>
         </is>
       </c>
       <c r="J37" s="6" t="n">
-        <v>15.9</v>
+        <v>70</v>
       </c>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
       <c r="M37" s="6" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N37" s="2" t="n"/>
+        <v>70</v>
+      </c>
+      <c r="N37" s="6" t="n">
+        <v>20.62</v>
+      </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>Frete grátis informado na página do produto: "🚚 FRETE GRÁTIS PARA TODO O BRASIL*" (sem calculadora de CEP no site)</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC R$ 26,55 5 dias úteis Jadlog Package R$ 40,39 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P37" s="2" t="n"/>
@@ -2813,7 +2829,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
@@ -2821,35 +2837,41 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
-        </is>
-      </c>
-      <c r="H38" s="2" t="n"/>
+          <t>27.061.442/0002-85</t>
+        </is>
+      </c>
+      <c r="H38" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lojas360.com.br/oculos-de-seguranca-urano</t>
+        </is>
+      </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>ÓCULOS SEGURANCA DISMA II INCOLOR</t>
-        </is>
-      </c>
-      <c r="J38" s="2" t="n"/>
+          <t>Óculos de Segurança Urano Incolor Anti Risco | C.A. 42547</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="n">
+        <v>9.41</v>
+      </c>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
-      <c r="M38" s="2" t="n"/>
-      <c r="N38" s="2" t="n"/>
+      <c r="M38" s="6" t="n">
+        <v>9.41</v>
+      </c>
+      <c r="N38" s="6" t="n">
+        <v>18.4</v>
+      </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
-        </is>
-      </c>
-      <c r="P38" s="5" t="inlineStr">
-        <is>
-          <t>https://www.supriflex.com.br/produto/oculos-seguranca-disma-ii-incolor.html</t>
-        </is>
-      </c>
+          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -2859,17 +2881,17 @@
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t>MÁSCARA DE PROTEÇÃO DESCARTÁVEL - USO CONFORME RISCO/ATIVIDADE.</t>
+          <t>ÓCULOS DE PROTEÇÃO INCOLOR - PARA MANIPULAÇÃO E APLICAÇÃO DE PRODUTOS QUÍMICOS.</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E39" s="4" t="n">
@@ -2877,36 +2899,38 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>ZEUS DO BRASIL LTDA (loja EPI Zeus)</t>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>82.699.588/0001-88</t>
+          <t>39.268.527/0001-37</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>https://www.epizeus.com.br/mascara-de-protec-o-pff1-sem-valvula-delta-plus-ca-38502</t>
+          <t>https://www.segurancatotal.com.br/produto/oculos-de-protecao-sky-deltaplus-incolor.html</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Máscara de Proteção PFF1 - Sem Válvula - CA 45020</t>
+          <t>Óculos De Proteção Sky Deltaplus Incolor</t>
         </is>
       </c>
       <c r="J39" s="6" t="n">
-        <v>1.9</v>
+        <v>3.99</v>
       </c>
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="6" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="N39" s="2" t="n"/>
+        <v>3.99</v>
+      </c>
+      <c r="N39" s="6" t="n">
+        <v>18.4</v>
+      </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>Frete grátis informado na página do produto: "🚚 FRETE GRÁTIS PARA TODO O BRASIL*" (sem calculadora de CEP no site)</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P39" s="2" t="n"/>
@@ -2919,54 +2943,54 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t>MÁSCARA DE PROTEÇÃO DESCARTÁVEL - USO CONFORME RISCO/ATIVIDADE.</t>
+          <t>ÓCULOS DE PROTEÇÃO INCOLOR - PARA MANIPULAÇÃO E APLICAÇÃO DE PRODUTOS QUÍMICOS.</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>Goiás Ferramentas</t>
+          <t>ZEUS DO BRASIL LTDA (loja EPI Zeus)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>09.497.806/0001-01</t>
+          <t>82.699.588/0001-88</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>https://www.goiasferramentas.com.br/produto/10985-mascara-descartavel-pff2-com-valvula</t>
+          <t>https://www.epizeus.com.br/oculos-protec-o-lente-incolor-policarbonato-ca-28018</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>MASCARA DESCARTAVEL PFF2 COM VALVULA</t>
+          <t>Óculos proteção lente incolor policarbonato - CA 10346</t>
         </is>
       </c>
       <c r="J40" s="6" t="n">
-        <v>1.9</v>
+        <v>15.9</v>
       </c>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="6" t="n">
-        <v>1.9</v>
+        <v>15.9</v>
       </c>
       <c r="N40" s="2" t="n"/>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO)</t>
+          <t>Frete grátis informado na página do produto: "🚚 FRETE GRÁTIS PARA TODO O BRASIL*" (sem calculadora de CEP no site)</t>
         </is>
       </c>
       <c r="P40" s="2" t="n"/>
@@ -2979,58 +3003,58 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t>MÁSCARA DE PROTEÇÃO DESCARTÁVEL - USO CONFORME RISCO/ATIVIDADE.</t>
+          <t>ÓCULOS DE PROTEÇÃO INCOLOR - PARA MANIPULAÇÃO E APLICAÇÃO DE PRODUTOS QUÍMICOS.</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>46307</v>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>Fermarcs Ferramentas</t>
+          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>08.615.223/0001-75</t>
+          <t>20.838.307/0001-73</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>https://www.fermarcsferramentas.com.br/epi-e-epc/respiratoria/mascara-de-protecao-msk95-pff-2-n95</t>
+          <t>https://www.lojadoepi.com.br/oculos-de-protecao-vvision-600-incolor-antiembacante-volk-ca-42922-p3187</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Mascara De Protecao Msk95 Pff-2 N95</t>
+          <t>Óculos de Proteção Vvision 600 Incolor Antiembaçante Volk CA 42922</t>
         </is>
       </c>
       <c r="J41" s="6" t="n">
-        <v>2.99</v>
+        <v>26.93</v>
       </c>
       <c r="K41" s="2" t="n"/>
-      <c r="L41" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: descartável.</t>
-        </is>
-      </c>
+      <c r="L41" s="2" t="n"/>
       <c r="M41" s="6" t="n">
-        <v>2.99</v>
-      </c>
-      <c r="N41" s="2" t="n"/>
+        <v>26.93</v>
+      </c>
+      <c r="N41" s="6" t="n">
+        <v>21.39</v>
+      </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO)</t>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 21,39 7 dia(s) útil(eis)</t>
         </is>
       </c>
       <c r="P41" s="2" t="n"/>
@@ -3043,17 +3067,17 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t>PROTETOR AURICULAR - PARA ATIVIDADES COM EXPOSIÇÃO A RUÍDO.</t>
+          <t>ÓCULOS DE PROTEÇÃO INCOLOR - PARA MANIPULAÇÃO E APLICAÇÃO DE PRODUTOS QUÍMICOS.</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
@@ -3061,41 +3085,35 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>27.061.442/0002-85</t>
-        </is>
-      </c>
-      <c r="H42" s="5" t="inlineStr">
-        <is>
-          <t>https://www.lojas360.com.br/protecao-auditiva/protetor-auditivo-tipo-plug-bicolor</t>
-        </is>
-      </c>
+          <t>46.412.993/0001-00</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="n"/>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>Protetor Auditivo Tipo Plug Bicolor Maxxi 18 dB| C.A. 11512</t>
-        </is>
-      </c>
-      <c r="J42" s="6" t="n">
-        <v>2.84</v>
-      </c>
+          <t>ÓCULOS SEGURANCA DISMA II INCOLOR</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n"/>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
-      <c r="M42" s="6" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="N42" s="6" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="M42" s="2" t="n"/>
+      <c r="N42" s="2" t="n"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
-        </is>
-      </c>
-      <c r="P42" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="inlineStr">
+        <is>
+          <t>https://www.supriflex.com.br/produto/oculos-seguranca-disma-ii-incolor.html</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3105,17 +3123,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>PROTETOR AURICULAR - PARA ATIVIDADES COM EXPOSIÇÃO A RUÍDO.</t>
+          <t>MÁSCARA DE PROTEÇÃO DESCARTÁVEL - USO CONFORME RISCO/ATIVIDADE.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
@@ -3123,38 +3141,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>SEGURANCA TOTAL EPIS LTDA</t>
+          <t>ZEUS DO BRASIL LTDA (loja EPI Zeus)</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>39.268.527/0001-37</t>
+          <t>82.699.588/0001-88</t>
         </is>
       </c>
       <c r="H43" s="5" t="inlineStr">
         <is>
-          <t>https://www.segurancatotal.com.br/produto/protetor-auricular-silicone-18db-protect.html</t>
+          <t>https://www.epizeus.com.br/mascara-de-protec-o-pff1-sem-valvula-delta-plus-ca-38502</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Protetor Auricular Silicone 18db Protect</t>
+          <t>Máscara de Proteção PFF1 - Sem Válvula - CA 45020</t>
         </is>
       </c>
       <c r="J43" s="6" t="n">
-        <v>1.99</v>
+        <v>1.9</v>
       </c>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
       <c r="M43" s="6" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="N43" s="6" t="n">
-        <v>18.4</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="N43" s="2" t="n"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
+          <t>Frete grátis informado na página do produto: "🚚 FRETE GRÁTIS PARA TODO O BRASIL*" (sem calculadora de CEP no site)</t>
         </is>
       </c>
       <c r="P43" s="2" t="n"/>
@@ -3167,56 +3183,54 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>PROTETOR AURICULAR - PARA ATIVIDADES COM EXPOSIÇÃO A RUÍDO.</t>
+          <t>MÁSCARA DE PROTEÇÃO DESCARTÁVEL - USO CONFORME RISCO/ATIVIDADE.</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>Goiás Ferramentas</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
+          <t>09.497.806/0001-01</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>https://www.supriflex.com.br/protetor-auricular-plug-k10-c-cordao-13db</t>
+          <t>https://www.goiasferramentas.com.br/produto/10985-mascara-descartavel-pff2-com-valvula</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>Protetor Auricular Plug k10 c/ Cordão 13DB</t>
+          <t>MASCARA DESCARTAVEL PFF2 COM VALVULA</t>
         </is>
       </c>
       <c r="J44" s="6" t="n">
-        <v>2.49</v>
+        <v>1.9</v>
       </c>
       <c r="K44" s="2" t="n"/>
       <c r="L44" s="2" t="n"/>
       <c r="M44" s="6" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="N44" s="6" t="n">
-        <v>31.54</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="N44" s="2" t="n"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 31,54 7 dias úteis Correios PAC R$ 36,14 8 dias úteis Correios - PAC R$ 41,80 6 dias úteis Jadlog - .Com</t>
+          <t>Frete não calculado (GO para GO)</t>
         </is>
       </c>
       <c r="P44" s="2" t="n"/>
@@ -3229,56 +3243,58 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>PROTETOR AURICULAR - PARA ATIVIDADES COM EXPOSIÇÃO A RUÍDO.</t>
+          <t>MÁSCARA DE PROTEÇÃO DESCARTÁVEL - USO CONFORME RISCO/ATIVIDADE.</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
+          <t>Fermarcs Ferramentas</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>20.838.307/0001-73</t>
+          <t>08.615.223/0001-75</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojadoepi.com.br/protetor-auricular-tipo-concha-pomp-muffler-3m-ca-14235-atenuacao-21db-228-p2585</t>
+          <t>https://www.fermarcsferramentas.com.br/epi-e-epc/respiratoria/mascara-de-protecao-msk95-pff-2-n95</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Protetor Auricular tipo Concha Pomp Muffler 3M CA 14235 atenuação 21db</t>
+          <t>Mascara De Protecao Msk95 Pff-2 N95</t>
         </is>
       </c>
       <c r="J45" s="6" t="n">
-        <v>154.94</v>
+        <v>2.99</v>
       </c>
       <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="n"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: descartável.</t>
+        </is>
+      </c>
       <c r="M45" s="6" t="n">
-        <v>154.94</v>
-      </c>
-      <c r="N45" s="6" t="n">
-        <v>23.77</v>
-      </c>
+        <v>2.99</v>
+      </c>
+      <c r="N45" s="2" t="n"/>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Pac R$ 23,77 7 dia(s) útil(eis)</t>
+          <t>Frete não calculado (GO para GO)</t>
         </is>
       </c>
       <c r="P45" s="2" t="n"/>
@@ -3291,54 +3307,58 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>1115</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>PROTETOR AURICULAR - PARA ATIVIDADES COM EXPOSIÇÃO A RUÍDO.</t>
+          <t>MÁSCARA DE PROTEÇÃO DESCARTÁVEL - USO CONFORME RISCO/ATIVIDADE.</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
-        </is>
-      </c>
-      <c r="E46" s="4" t="n">
-        <v>46304</v>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>Goiás Ferramentas</t>
+          <t>TR Distribuidora de Equipamentos de Segurança LTDA</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>09.497.806/0001-01</t>
+          <t>14.213.841/0001-91</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>https://www.goiasferramentas.com.br/produto/424-protetor-auricular-tipo-plug-em-silicone-14db-kalipso-ca-14470</t>
+          <t>https://www.trepis.com.br/mascara-descartavel-confec-em-tnt-tripla-branca-com-elastico-pct-c50un</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Protetor Auricular Tipo Plug em Silicone 14dB Kalipso CA 14470</t>
+          <t>Máscara Descartável Tripla TNT Branca com Elástico Pacote com 50 Unidades</t>
         </is>
       </c>
       <c r="J46" s="6" t="n">
-        <v>2.06</v>
+        <v>10.81</v>
       </c>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
       <c r="M46" s="6" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="N46" s="2" t="n"/>
+        <v>10.81</v>
+      </c>
+      <c r="N46" s="6" t="n">
+        <v>21.55</v>
+      </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO)</t>
+          <t>Opção mais barata para o CEP 74933-130: JADLOG .Package R$ 21,55 Capital de todo Brasil: 01 a 03 dias. Interior de Todo Brasil: 02 a 05 dias.</t>
         </is>
       </c>
       <c r="P46" s="2" t="n"/>
@@ -3351,60 +3371,58 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1114</t>
         </is>
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>AVENTAL DE PVC - IMPERMEÁVEL, PARA ATIVIDADES COM RISCO DE RESPINGOS.</t>
+          <t>MÁSCARA DE PROTEÇÃO DESCARTÁVEL - USO CONFORME RISCO/ATIVIDADE.</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E47" s="4" t="n">
-        <v>46308</v>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+          <t>ASTRO DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>27.061.442/0002-85</t>
+          <t>18.597.685/0001-60</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojas360.com.br/vestimentas/avental-de-pvc-forrado-com-ihos-1649?variant_id=5583</t>
+          <t>https://www.astrodistribuidora.com/mascara-de-tnt-descartavel-com-elastico-volk</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Avental de PVC Forrado com Ihós 1,20 X 0,70 - C.A. 21075</t>
+          <t>Máscara de TNT Descartável com Elástico - Volk (100 Unidades)</t>
         </is>
       </c>
       <c r="J47" s="6" t="n">
-        <v>8.460000000000001</v>
+        <v>10.42</v>
       </c>
       <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="inlineStr">
-        <is>
-          <t>PVC aceito como impermeável (equivalência).</t>
-        </is>
-      </c>
+      <c r="L47" s="2" t="n"/>
       <c r="M47" s="6" t="n">
-        <v>8.460000000000001</v>
+        <v>10.42</v>
       </c>
       <c r="N47" s="6" t="n">
-        <v>18.4</v>
+        <v>26.82</v>
       </c>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
+          <t>Opção mais barata para o CEP 74933-130: JADLOG - Entrega em até 5 dias úteis - R$26,82 BRASPRESS - Entrega em até 15 dias úteis -</t>
         </is>
       </c>
       <c r="P47" s="2" t="n"/>
@@ -3417,12 +3435,12 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>AVENTAL DE PVC - IMPERMEÁVEL, PARA ATIVIDADES COM RISCO DE RESPINGOS.</t>
+          <t>PROTETOR AURICULAR - PARA ATIVIDADES COM EXPOSIÇÃO A RUÍDO.</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3435,42 +3453,38 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>SEGURANCA TOTAL EPIS LTDA</t>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>39.268.527/0001-37</t>
+          <t>27.061.442/0002-85</t>
         </is>
       </c>
       <c r="H48" s="5" t="inlineStr">
         <is>
-          <t>https://www.segurancatotal.com.br/avental-pvc-forrado-c-fivela-preto-120-x-065-ca38302</t>
+          <t>https://www.lojas360.com.br/protecao-auditiva/protetor-auditivo-tipo-plug-bicolor</t>
         </is>
       </c>
       <c r="I48" s="3" t="inlineStr">
         <is>
-          <t>Avental Pvc Forrado C Fivela Preto Brascamp</t>
+          <t>Protetor Auditivo Tipo Plug Bicolor Maxxi 18 dB| C.A. 11512</t>
         </is>
       </c>
       <c r="J48" s="6" t="n">
-        <v>16.11</v>
+        <v>2.84</v>
       </c>
       <c r="K48" s="2" t="n"/>
-      <c r="L48" s="2" t="inlineStr">
-        <is>
-          <t>PVC aceito como impermeável (equivalência).</t>
-        </is>
-      </c>
+      <c r="L48" s="2" t="n"/>
       <c r="M48" s="6" t="n">
-        <v>16.11</v>
+        <v>2.84</v>
       </c>
       <c r="N48" s="6" t="n">
         <v>18.4</v>
       </c>
       <c r="O48" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
+          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
         </is>
       </c>
       <c r="P48" s="2" t="n"/>
@@ -3483,17 +3497,17 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>AVENTAL DE PVC - IMPERMEÁVEL, PARA ATIVIDADES COM RISCO DE RESPINGOS.</t>
+          <t>PROTETOR AURICULAR - PARA ATIVIDADES COM EXPOSIÇÃO A RUÍDO.</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E49" s="4" t="n">
@@ -3501,40 +3515,38 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>ZEUS DO BRASIL LTDA (loja EPI Zeus)</t>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>82.699.588/0001-88</t>
+          <t>39.268.527/0001-37</t>
         </is>
       </c>
       <c r="H49" s="5" t="inlineStr">
         <is>
-          <t>https://www.epizeus.com.br/avental-pvc-branco-forrado-com-bainha-120x70-cm-ca-37729</t>
+          <t>https://www.segurancatotal.com.br/produto/protetor-auricular-silicone-18db-protect.html</t>
         </is>
       </c>
       <c r="I49" s="3" t="inlineStr">
         <is>
-          <t>Avental PVC branco forrado com bainha 120x70 cm - CA 37729</t>
+          <t>Protetor Auricular Silicone 18db Protect</t>
         </is>
       </c>
       <c r="J49" s="6" t="n">
-        <v>15.9</v>
+        <v>1.99</v>
       </c>
       <c r="K49" s="2" t="n"/>
-      <c r="L49" s="2" t="inlineStr">
-        <is>
-          <t>PVC aceito como impermeável (equivalência).</t>
-        </is>
-      </c>
+      <c r="L49" s="2" t="n"/>
       <c r="M49" s="6" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N49" s="2" t="n"/>
+        <v>1.99</v>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>18.4</v>
+      </c>
       <c r="O49" s="3" t="inlineStr">
         <is>
-          <t>Frete grátis informado na página do produto: "🚚 FRETE GRÁTIS PARA TODO O BRASIL*" (sem calculadora de CEP no site)</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P49" s="2" t="n"/>
@@ -3547,17 +3559,17 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>AVENTAL DE PVC - IMPERMEÁVEL, PARA ATIVIDADES COM RISCO DE RESPINGOS.</t>
+          <t>PROTETOR AURICULAR - PARA ATIVIDADES COM EXPOSIÇÃO A RUÍDO.</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E50" s="4" t="n">
@@ -3565,42 +3577,38 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>ASTRO DISTRIBUIDORA LTDA</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>18.597.685/0001-60</t>
+          <t>46.412.993/0001-00</t>
         </is>
       </c>
       <c r="H50" s="5" t="inlineStr">
         <is>
-          <t>https://www.astrodistribuidora.com/avental-de-pvc-com-forro-115x065-cm-branco-048mm-maicol-ca-40172</t>
+          <t>https://www.supriflex.com.br/protetor-auricular-plug-k10-c-cordao-13db</t>
         </is>
       </c>
       <c r="I50" s="3" t="inlineStr">
         <is>
-          <t>Avental de PVC com Forro 1,15 x 0,65 cm Branco 0,48 mm - Maicol | CA - 40172</t>
+          <t>Protetor Auricular Plug k10 c/ Cordão 13DB</t>
         </is>
       </c>
       <c r="J50" s="6" t="n">
-        <v>3.09</v>
+        <v>2.49</v>
       </c>
       <c r="K50" s="2" t="n"/>
-      <c r="L50" s="2" t="inlineStr">
-        <is>
-          <t>PVC aceito como impermeável (equivalência).</t>
-        </is>
-      </c>
+      <c r="L50" s="2" t="n"/>
       <c r="M50" s="6" t="n">
-        <v>3.09</v>
+        <v>2.49</v>
       </c>
       <c r="N50" s="6" t="n">
-        <v>28.86</v>
+        <v>31.54</v>
       </c>
       <c r="O50" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: JADLOG - Entrega em até 5 dias úteis - R$28,86 BRASPRESS - Entrega em até 15 dias úteis - R$46,85</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 31,54 7 dias úteis Correios PAC R$ 36,14 8 dias úteis Correios - PAC R$ 41,80 6 dias úteis Jadlog - .Com</t>
         </is>
       </c>
       <c r="P50" s="2" t="n"/>
@@ -3613,56 +3621,56 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>AVENTAL DE PVC - IMPERMEÁVEL, PARA ATIVIDADES COM RISCO DE RESPINGOS.</t>
+          <t>PROTETOR AURICULAR - PARA ATIVIDADES COM EXPOSIÇÃO A RUÍDO.</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E51" s="4" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>Multiseg Comercio de Equipamentos de Seguranca Ltda</t>
+          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>10.498.304/0001-84</t>
+          <t>20.838.307/0001-73</t>
         </is>
       </c>
       <c r="H51" s="5" t="inlineStr">
         <is>
-          <t>https://www.multiseg.com.br/3484/avental-pvc-preto-com-tiras-e-fivela-120-x-70-cm-ca-38302-maicol</t>
+          <t>https://www.lojadoepi.com.br/protetor-auricular-tipo-concha-pomp-muffler-3m-ca-14235-atenuacao-21db-228-p2585</t>
         </is>
       </c>
       <c r="I51" s="3" t="inlineStr">
         <is>
-          <t>Avental de Segurança Pvc Impermeável 1,15X0,65M Ca 38302</t>
+          <t>Protetor Auricular tipo Concha Pomp Muffler 3M CA 14235 atenuação 21db</t>
         </is>
       </c>
       <c r="J51" s="6" t="n">
-        <v>9.869999999999999</v>
+        <v>154.94</v>
       </c>
       <c r="K51" s="2" t="n"/>
       <c r="L51" s="2" t="n"/>
       <c r="M51" s="6" t="n">
-        <v>9.869999999999999</v>
+        <v>154.94</v>
       </c>
       <c r="N51" s="6" t="n">
-        <v>32.85</v>
+        <v>23.77</v>
       </c>
       <c r="O51" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Pac R$ 32,85 De 9 A 10 dia(s) Úteis</t>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 23,77 7 dia(s) útil(eis)</t>
         </is>
       </c>
       <c r="P51" s="2" t="n"/>
@@ -3675,57 +3683,57 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>1116</t>
+          <t>1115</t>
         </is>
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>AVENTAL DE PVC - IMPERMEÁVEL, PARA ATIVIDADES COM RISCO DE RESPINGOS.</t>
+          <t>PROTETOR AURICULAR - PARA ATIVIDADES COM EXPOSIÇÃO A RUÍDO.</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>DF</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E52" s="4" t="n">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>HP Máquinas (HP Eletrotécnica Comércio Manutenção)</t>
+          <t>Goiás Ferramentas</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>09.636.445/0001-37</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="n"/>
+          <t>09.497.806/0001-01</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>https://www.goiasferramentas.com.br/produto/424-protetor-auricular-tipo-plug-em-silicone-14db-kalipso-ca-14470</t>
+        </is>
+      </c>
       <c r="I52" s="3" t="inlineStr">
         <is>
-          <t>Avental PVC Kp400 1,20x0,65- BRASCAM C.A. 37785</t>
-        </is>
-      </c>
-      <c r="J52" s="2" t="n"/>
+          <t>Protetor Auricular Tipo Plug em Silicone 14dB Kalipso CA 14470</t>
+        </is>
+      </c>
+      <c r="J52" s="6" t="n">
+        <v>2.06</v>
+      </c>
       <c r="K52" s="2" t="n"/>
-      <c r="L52" s="2" t="inlineStr">
-        <is>
-          <t>PVC aceito como impermeável (equivalência).</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="n"/>
+      <c r="L52" s="2" t="n"/>
+      <c r="M52" s="6" t="n">
+        <v>2.06</v>
+      </c>
       <c r="N52" s="2" t="n"/>
       <c r="O52" s="3" t="inlineStr">
         <is>
-          <t>Frete a coletar manualmente: o print não mostra o frete para o CEP 74933-130 (preço na página: R$ 26,90)</t>
-        </is>
-      </c>
-      <c r="P52" s="5" t="inlineStr">
-        <is>
-          <t>https://www.hpmaquinas.com.br/epi-equipamento-de-protecao-individual/avental-pvc-kp400-1-20x0-65-brascam-c-a-37785</t>
-        </is>
-      </c>
+          <t>Frete não calculado (GO para GO)</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -3745,7 +3753,7 @@
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E53" s="4" t="n">
@@ -3753,39 +3761,45 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
-        </is>
-      </c>
-      <c r="H53" s="2" t="n"/>
+          <t>27.061.442/0002-85</t>
+        </is>
+      </c>
+      <c r="H53" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lojas360.com.br/vestimentas/avental-de-pvc-forrado-com-ihos-1649?variant_id=5583</t>
+        </is>
+      </c>
       <c r="I53" s="3" t="inlineStr">
         <is>
-          <t>Avental PVC 120x70cm</t>
-        </is>
-      </c>
-      <c r="J53" s="2" t="n"/>
+          <t>Avental de PVC Forrado com Ihós 1,20 X 0,70 - C.A. 21075</t>
+        </is>
+      </c>
+      <c r="J53" s="6" t="n">
+        <v>8.460000000000001</v>
+      </c>
       <c r="K53" s="2" t="n"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
           <t>PVC aceito como impermeável (equivalência).</t>
         </is>
       </c>
-      <c r="M53" s="2" t="n"/>
-      <c r="N53" s="2" t="n"/>
+      <c r="M53" s="6" t="n">
+        <v>8.460000000000001</v>
+      </c>
+      <c r="N53" s="6" t="n">
+        <v>18.4</v>
+      </c>
       <c r="O53" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
-        </is>
-      </c>
-      <c r="P53" s="5" t="inlineStr">
-        <is>
-          <t>https://www.supriflex.com.br/avental-pvc-120x70cm</t>
-        </is>
-      </c>
+          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -3805,7 +3819,7 @@
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E54" s="4" t="n">
@@ -3813,31 +3827,45 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>A MASTER ARTIGOS PARA PROTECAO INDIVIDUAL E INDUSTRIAL LTDA (A Master EPI)</t>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>16.603.654/0001-40</t>
-        </is>
-      </c>
-      <c r="H54" s="2" t="n"/>
-      <c r="I54" s="3" t="n"/>
-      <c r="J54" s="2" t="n"/>
+          <t>39.268.527/0001-37</t>
+        </is>
+      </c>
+      <c r="H54" s="5" t="inlineStr">
+        <is>
+          <t>https://www.segurancatotal.com.br/avental-pvc-forrado-c-fivela-preto-120-x-065-ca38302</t>
+        </is>
+      </c>
+      <c r="I54" s="3" t="inlineStr">
+        <is>
+          <t>Avental Pvc Forrado C Fivela Preto Brascamp</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="n">
+        <v>16.11</v>
+      </c>
       <c r="K54" s="2" t="n"/>
-      <c r="L54" s="2" t="n"/>
-      <c r="M54" s="2" t="n"/>
-      <c r="N54" s="2" t="n"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>PVC aceito como impermeável (equivalência).</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>16.11</v>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>18.4</v>
+      </c>
       <c r="O54" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
-        </is>
-      </c>
-      <c r="P54" s="5" t="inlineStr">
-        <is>
-          <t>https://www.amasterepi.com.br/busca?q=Avental%20De%20Pvc</t>
-        </is>
-      </c>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -3847,17 +3875,17 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>CAPA DE CHUVA - PVC IMPERMEÁVEL, COM CAPUZ E COSTURAS SELADAS.</t>
+          <t>AVENTAL DE PVC - IMPERMEÁVEL, PARA ATIVIDADES COM RISCO DE RESPINGOS.</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E55" s="4" t="n">
@@ -3865,42 +3893,40 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+          <t>ZEUS DO BRASIL LTDA (loja EPI Zeus)</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>27.061.442/0002-85</t>
+          <t>82.699.588/0001-88</t>
         </is>
       </c>
       <c r="H55" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojas360.com.br/vestimentas/conjunto-de-motoqueiro?variant_id=4633</t>
+          <t>https://www.epizeus.com.br/avental-pvc-branco-forrado-com-bainha-120x70-cm-ca-37729</t>
         </is>
       </c>
       <c r="I55" s="3" t="inlineStr">
         <is>
-          <t>Capa de Chuva Motoqueiro Conjunto Impermeável</t>
+          <t>Avental PVC branco forrado com bainha 120x70 cm - CA 37729</t>
         </is>
       </c>
       <c r="J55" s="6" t="n">
-        <v>85.09</v>
+        <v>15.9</v>
       </c>
       <c r="K55" s="2" t="n"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: PVC, capuz, costuras seladas.</t>
+          <t>PVC aceito como impermeável (equivalência).</t>
         </is>
       </c>
       <c r="M55" s="6" t="n">
-        <v>85.09</v>
-      </c>
-      <c r="N55" s="6" t="n">
-        <v>21.9</v>
-      </c>
+        <v>15.9</v>
+      </c>
+      <c r="N55" s="2" t="n"/>
       <c r="O55" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 31,27 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 21,90 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
+          <t>Frete grátis informado na página do produto: "🚚 FRETE GRÁTIS PARA TODO O BRASIL*" (sem calculadora de CEP no site)</t>
         </is>
       </c>
       <c r="P55" s="2" t="n"/>
@@ -3913,60 +3939,60 @@
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>CAPA DE CHUVA - PVC IMPERMEÁVEL, COM CAPUZ E COSTURAS SELADAS.</t>
+          <t>AVENTAL DE PVC - IMPERMEÁVEL, PARA ATIVIDADES COM RISCO DE RESPINGOS.</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E56" s="4" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>Loja do EPI</t>
+          <t>ASTRO DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>20.838.307/0001-73</t>
+          <t>18.597.685/0001-60</t>
         </is>
       </c>
       <c r="H56" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojadoepi.com.br/capa-de-chuva-em-pvc-forrado-preto-com-capuz-ca-49932-p2065?pp=/40.1487/</t>
+          <t>https://www.astrodistribuidora.com/avental-de-pvc-com-forro-115x065-cm-branco-048mm-maicol-ca-40172</t>
         </is>
       </c>
       <c r="I56" s="3" t="inlineStr">
         <is>
-          <t>Capa De Chuva Pvc Preta Ca 49932</t>
+          <t>Avental de PVC com Forro 1,15 x 0,65 cm Branco 0,48 mm - Maicol | CA - 40172</t>
         </is>
       </c>
       <c r="J56" s="6" t="n">
-        <v>20.91</v>
+        <v>3.09</v>
       </c>
       <c r="K56" s="2" t="n"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: costuras seladas.</t>
+          <t>PVC aceito como impermeável (equivalência).</t>
         </is>
       </c>
       <c r="M56" s="6" t="n">
-        <v>20.91</v>
+        <v>3.09</v>
       </c>
       <c r="N56" s="6" t="n">
-        <v>21.39</v>
+        <v>28.86</v>
       </c>
       <c r="O56" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Pac R$ 21,39</t>
+          <t>Opção mais barata para o CEP 74933-130: JADLOG - Entrega em até 5 dias úteis - R$28,86 BRASPRESS - Entrega em até 15 dias úteis - R$46,85</t>
         </is>
       </c>
       <c r="P56" s="2" t="n"/>
@@ -3979,17 +4005,17 @@
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>CAPA DE CHUVA - PVC IMPERMEÁVEL, COM CAPUZ E COSTURAS SELADAS.</t>
+          <t>AVENTAL DE PVC - IMPERMEÁVEL, PARA ATIVIDADES COM RISCO DE RESPINGOS.</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E57" s="4" t="n">
@@ -3997,42 +4023,38 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>A Master EPI</t>
+          <t>Multiseg Comercio de Equipamentos de Seguranca Ltda</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>16.603.654/0001-40</t>
+          <t>10.498.304/0001-84</t>
         </is>
       </c>
       <c r="H57" s="5" t="inlineStr">
         <is>
-          <t>https://www.amasterepi.com.br/19430/capa-de-chuva-pvc-cforro-stand</t>
+          <t>https://www.multiseg.com.br/3484/avental-pvc-preto-com-tiras-e-fivela-120-x-70-cm-ca-38302-maicol</t>
         </is>
       </c>
       <c r="I57" s="3" t="inlineStr">
         <is>
-          <t>Capa de Chuva Pvc C/Forro Stand</t>
+          <t>Avental de Segurança Pvc Impermeável 1,15X0,65M Ca 38302</t>
         </is>
       </c>
       <c r="J57" s="6" t="n">
-        <v>18</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="K57" s="2" t="n"/>
-      <c r="L57" s="2" t="inlineStr">
-        <is>
-          <t>Costura "através de solda eletrônica" (página do produto) aceita como costura selada; equivalência não confirmada pelo fabricante (decisão de 13/10/2026).</t>
-        </is>
-      </c>
+      <c r="L57" s="2" t="n"/>
       <c r="M57" s="6" t="n">
-        <v>18</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="N57" s="6" t="n">
         <v>32.85</v>
       </c>
       <c r="O57" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Entrega Econômica R$ 32,85 De 6 A 7 dia(s) Úteis</t>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 32,85 De 9 A 10 dia(s) Úteis</t>
         </is>
       </c>
       <c r="P57" s="2" t="n"/>
@@ -4045,17 +4067,17 @@
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>1117</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>CAPA DE CHUVA - PVC IMPERMEÁVEL, COM CAPUZ E COSTURAS SELADAS.</t>
+          <t>AVENTAL DE PVC - IMPERMEÁVEL, PARA ATIVIDADES COM RISCO DE RESPINGOS.</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>DF</t>
         </is>
       </c>
       <c r="E58" s="4" t="n">
@@ -4063,33 +4085,37 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>HP Máquinas (HP Eletrotécnica Comércio Manutenção)</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
+          <t>09.636.445/0001-37</t>
         </is>
       </c>
       <c r="H58" s="2" t="n"/>
       <c r="I58" s="3" t="inlineStr">
         <is>
-          <t>CAPA P/ CHUVA PVC MORCEGO C/CAPUZ GRANDE AMARELA</t>
+          <t>Avental PVC Kp400 1,20x0,65- BRASCAM C.A. 37785</t>
         </is>
       </c>
       <c r="J58" s="2" t="n"/>
       <c r="K58" s="2" t="n"/>
-      <c r="L58" s="2" t="n"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>PVC aceito como impermeável (equivalência).</t>
+        </is>
+      </c>
       <c r="M58" s="2" t="n"/>
       <c r="N58" s="2" t="n"/>
       <c r="O58" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
+          <t>Frete a coletar manualmente: o print não mostra o frete para o CEP 74933-130 (preço na página: R$ 26,90)</t>
         </is>
       </c>
       <c r="P58" s="5" t="inlineStr">
         <is>
-          <t>https://www.supriflex.com.br/produto/capa-pvc-morcego-ccapuz-grande-amarela.html</t>
+          <t>https://www.hpmaquinas.com.br/epi-equipamento-de-protecao-individual/avental-pvc-kp400-1-20x0-65-brascam-c-a-37785</t>
         </is>
       </c>
     </row>
@@ -4101,17 +4127,17 @@
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="C59" s="3" t="inlineStr">
         <is>
-          <t>BONÉ ÁRABE/SOMBREIRO PARA PROTEÇÃO SOLAR - PARA SERVIÇOS EXTERNOS.</t>
+          <t>AVENTAL DE PVC - IMPERMEÁVEL, PARA ATIVIDADES COM RISCO DE RESPINGOS.</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E59" s="4" t="n">
@@ -4119,41 +4145,39 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>20.838.307/0001-73</t>
-        </is>
-      </c>
-      <c r="H59" s="5" t="inlineStr">
-        <is>
-          <t>https://www.lojadoepi.com.br/bone-arabe-helanca-azul-ca-39856-pr-22257-ca-39856-p4964</t>
-        </is>
-      </c>
+          <t>46.412.993/0001-00</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="n"/>
       <c r="I59" s="3" t="inlineStr">
         <is>
-          <t>Bone Arabe Helanca Azul Ca 39856</t>
-        </is>
-      </c>
-      <c r="J59" s="6" t="n">
-        <v>11.47</v>
-      </c>
+          <t>Avental PVC 120x70cm</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n"/>
       <c r="K59" s="2" t="n"/>
-      <c r="L59" s="2" t="n"/>
-      <c r="M59" s="6" t="n">
-        <v>11.47</v>
-      </c>
-      <c r="N59" s="6" t="n">
-        <v>21.39</v>
-      </c>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>PVC aceito como impermeável (equivalência).</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="n"/>
+      <c r="N59" s="2" t="n"/>
       <c r="O59" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Pac R$ 21,39 7 dia(s) útil(eis)</t>
-        </is>
-      </c>
-      <c r="P59" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P59" s="5" t="inlineStr">
+        <is>
+          <t>https://www.supriflex.com.br/avental-pvc-120x70cm</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4163,12 +4187,12 @@
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1116</t>
         </is>
       </c>
       <c r="C60" s="3" t="inlineStr">
         <is>
-          <t>BONÉ ÁRABE/SOMBREIRO PARA PROTEÇÃO SOLAR - PARA SERVIÇOS EXTERNOS.</t>
+          <t>AVENTAL DE PVC - IMPERMEÁVEL, PARA ATIVIDADES COM RISCO DE RESPINGOS.</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -4181,41 +4205,31 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>TR Distribuidora de Equipamentos de Segurança LTDA</t>
+          <t>A MASTER ARTIGOS PARA PROTECAO INDIVIDUAL E INDUSTRIAL LTDA (A Master EPI)</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>14.213.841/0001-91</t>
-        </is>
-      </c>
-      <c r="H60" s="5" t="inlineStr">
-        <is>
-          <t>https://www.trepis.com.br/bone-arabe-em-brim-com-velcro-para-protecao-solar-azul-ca-49731</t>
-        </is>
-      </c>
-      <c r="I60" s="3" t="inlineStr">
-        <is>
-          <t>Boné Árabe em Brim com Velcro para Proteção Solar Azul C.A. 49731</t>
-        </is>
-      </c>
-      <c r="J60" s="6" t="n">
-        <v>18.38</v>
-      </c>
+          <t>16.603.654/0001-40</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="n"/>
+      <c r="I60" s="3" t="n"/>
+      <c r="J60" s="2" t="n"/>
       <c r="K60" s="2" t="n"/>
       <c r="L60" s="2" t="n"/>
-      <c r="M60" s="6" t="n">
-        <v>18.38</v>
-      </c>
-      <c r="N60" s="6" t="n">
-        <v>21.55</v>
-      </c>
+      <c r="M60" s="2" t="n"/>
+      <c r="N60" s="2" t="n"/>
       <c r="O60" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: PAC R$ 27,59 7 dias úteis. JADLOG .Package R$ 21,55 Capital de todo Brasil: 01 a 03 dias. Interior de Todo Brasil: 02 a 05 dias. JADLOG Econômico R$ 7</t>
-        </is>
-      </c>
-      <c r="P60" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P60" s="5" t="inlineStr">
+        <is>
+          <t>https://www.amasterepi.com.br/busca?q=Avental%20De%20Pvc</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4225,54 +4239,60 @@
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
         <is>
-          <t>BONÉ ÁRABE/SOMBREIRO PARA PROTEÇÃO SOLAR - PARA SERVIÇOS EXTERNOS.</t>
+          <t>CAPA DE CHUVA - PVC IMPERMEÁVEL, COM CAPUZ E COSTURAS SELADAS.</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E61" s="4" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>Fermarcs Ferramentas</t>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>08.615.223/0001-75</t>
+          <t>27.061.442/0002-85</t>
         </is>
       </c>
       <c r="H61" s="5" t="inlineStr">
         <is>
-          <t>https://www.fermarcsferramentas.com.br/equipamentos-de-protecao/acessorios-para-cabeca/bone-arabe-poliester-stela</t>
+          <t>https://www.lojas360.com.br/vestimentas/conjunto-de-motoqueiro?variant_id=4633</t>
         </is>
       </c>
       <c r="I61" s="3" t="inlineStr">
         <is>
-          <t>Bone Arabe Poliester S/Tela</t>
+          <t>Capa de Chuva Motoqueiro Conjunto Impermeável</t>
         </is>
       </c>
       <c r="J61" s="6" t="n">
-        <v>17.5</v>
+        <v>85.09</v>
       </c>
       <c r="K61" s="2" t="n"/>
-      <c r="L61" s="2" t="n"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: PVC, capuz, costuras seladas.</t>
+        </is>
+      </c>
       <c r="M61" s="6" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="N61" s="2" t="n"/>
+        <v>85.09</v>
+      </c>
+      <c r="N61" s="6" t="n">
+        <v>21.9</v>
+      </c>
       <c r="O61" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO)</t>
+          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 31,27 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 21,90 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
         </is>
       </c>
       <c r="P61" s="2" t="n"/>
@@ -4285,56 +4305,60 @@
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="C62" s="3" t="inlineStr">
         <is>
-          <t>BONÉ ÁRABE/SOMBREIRO PARA PROTEÇÃO SOLAR - PARA SERVIÇOS EXTERNOS.</t>
+          <t>CAPA DE CHUVA - PVC IMPERMEÁVEL, COM CAPUZ E COSTURAS SELADAS.</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E62" s="4" t="n">
-        <v>46304</v>
+        <v>46306</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>A Master EPI</t>
+          <t>Loja do EPI</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>16.603.654/0001-40</t>
+          <t>20.838.307/0001-73</t>
         </is>
       </c>
       <c r="H62" s="5" t="inlineStr">
         <is>
-          <t>https://www.amasterepi.com.br/19167/bone-arabe-azul-helanca-c-protecao-pescoco-prime</t>
+          <t>https://www.lojadoepi.com.br/capa-de-chuva-em-pvc-forrado-preto-com-capuz-ca-49932-p2065?pp=/40.1487/</t>
         </is>
       </c>
       <c r="I62" s="3" t="inlineStr">
         <is>
-          <t>Bone Arabe Azul Helanca C/ Protecao Pescoço Prime</t>
+          <t>Capa De Chuva Pvc Preta Ca 49932</t>
         </is>
       </c>
       <c r="J62" s="6" t="n">
-        <v>12</v>
+        <v>20.91</v>
       </c>
       <c r="K62" s="2" t="n"/>
-      <c r="L62" s="2" t="n"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: costuras seladas.</t>
+        </is>
+      </c>
       <c r="M62" s="6" t="n">
-        <v>12</v>
+        <v>20.91</v>
       </c>
       <c r="N62" s="6" t="n">
-        <v>32.85</v>
+        <v>21.39</v>
       </c>
       <c r="O62" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Entrega Econômica R$ 32,85 De 6 A 7 dia(s) Úteis</t>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 21,39</t>
         </is>
       </c>
       <c r="P62" s="2" t="n"/>
@@ -4347,56 +4371,62 @@
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>1118</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="C63" s="3" t="inlineStr">
         <is>
-          <t>BONÉ ÁRABE/SOMBREIRO PARA PROTEÇÃO SOLAR - PARA SERVIÇOS EXTERNOS.</t>
+          <t>CAPA DE CHUVA - PVC IMPERMEÁVEL, COM CAPUZ E COSTURAS SELADAS.</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E63" s="4" t="n">
-        <v>46307</v>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>ZEUS DO BRASIL</t>
+          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>82.699.588/0001-88</t>
+          <t>31.893.116/0001-20</t>
         </is>
       </c>
       <c r="H63" s="5" t="inlineStr">
         <is>
-          <t>https://www.shoppingdaseguranca.com.br/touca-arabe-helanca-cinza-bone</t>
+          <t>https://www.loja.bhzepi.com.br/produto/capa-de-chuva-pvc-amarelo-forrado-tamanho-g.html</t>
         </is>
       </c>
       <c r="I63" s="3" t="inlineStr">
         <is>
-          <t>Touca Árabe Tipo Boné em Helanca Cinza</t>
+          <t>Capa De Chuva Pvc Amarelo Forrado Tamanho G</t>
         </is>
       </c>
       <c r="J63" s="6" t="n">
-        <v>17.9</v>
+        <v>25</v>
       </c>
       <c r="K63" s="2" t="n"/>
-      <c r="L63" s="2" t="n"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>Costura 'através de solda eletrônica' aceita como costura selada; equivalência não confirmada pelo fabricante (decisão de 13/10/2026).</t>
+        </is>
+      </c>
       <c r="M63" s="6" t="n">
-        <v>17.9</v>
+        <v>25</v>
       </c>
       <c r="N63" s="6" t="n">
-        <v>61.87</v>
+        <v>20.62</v>
       </c>
       <c r="O63" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Entrega Econômica 8 dias úteis R$ 61,87</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC</t>
         </is>
       </c>
       <c r="P63" s="2" t="n"/>
@@ -4409,54 +4439,60 @@
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="C64" s="3" t="inlineStr">
         <is>
-          <t>BLOQUEADOR/PROTETOR SOLAR FPS 30 OU 50 - PARA SERVIÇOS EXTERNOS; MANTER COMO ITEM DE PROTEÇÃO OCUPACIONAL NA COMPOSIÇÃO.</t>
+          <t>CAPA DE CHUVA - PVC IMPERMEÁVEL, COM CAPUZ E COSTURAS SELADAS.</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E64" s="4" t="n">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
+          <t>A Master EPI</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>31.893.116/0001-20</t>
+          <t>16.603.654/0001-40</t>
         </is>
       </c>
       <c r="H64" s="5" t="inlineStr">
         <is>
-          <t>https://www.loja.bhzepi.com.br/protetor-solar-sunlau-30-fps-de-1kg</t>
+          <t>https://www.amasterepi.com.br/19430/capa-de-chuva-pvc-cforro-stand</t>
         </is>
       </c>
       <c r="I64" s="3" t="inlineStr">
         <is>
-          <t>PROTETOR SOLAR PARA PRAIA SUNLAU 30 FPS DE 1KG</t>
+          <t>Capa de Chuva Pvc C/Forro Stand</t>
         </is>
       </c>
       <c r="J64" s="6" t="n">
-        <v>121.9</v>
+        <v>18</v>
       </c>
       <c r="K64" s="2" t="n"/>
-      <c r="L64" s="2" t="n"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>Costura "através de solda eletrônica" (página do produto) aceita como costura selada; equivalência não confirmada pelo fabricante (decisão de 13/10/2026).</t>
+        </is>
+      </c>
       <c r="M64" s="6" t="n">
-        <v>121.9</v>
-      </c>
-      <c r="N64" s="2" t="n"/>
+        <v>18</v>
+      </c>
+      <c r="N64" s="6" t="n">
+        <v>32.85</v>
+      </c>
       <c r="O64" s="3" t="inlineStr">
         <is>
-          <t>Frete grátis para o CEP 74933-130</t>
+          <t>Opção mais barata para o CEP 74933-130: Entrega Econômica R$ 32,85 De 6 A 7 dia(s) Úteis</t>
         </is>
       </c>
       <c r="P64" s="2" t="n"/>
@@ -4469,12 +4505,12 @@
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>BLOQUEADOR/PROTETOR SOLAR FPS 30 OU 50 - PARA SERVIÇOS EXTERNOS; MANTER COMO ITEM DE PROTEÇÃO OCUPACIONAL NA COMPOSIÇÃO.</t>
+          <t>CAPA DE CHUVA - PVC IMPERMEÁVEL, COM CAPUZ E COSTURAS SELADAS.</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4482,43 +4518,49 @@
           <t>SP</t>
         </is>
       </c>
-      <c r="E65" s="4" t="n">
-        <v>46308</v>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
-          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
         </is>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t>27.061.442/0002-85</t>
+          <t>39.268.527/0001-37</t>
         </is>
       </c>
       <c r="H65" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojas360.com.br/protecao-solar/protetor-solar-fps-30-com-vitamina-e-1kg</t>
+          <t>https://www.segurancatotal.com.br/produto/capa-de-chuva-policap-pvc-forrado-azul.html</t>
         </is>
       </c>
       <c r="I65" s="3" t="inlineStr">
         <is>
-          <t>Protetor Solar FPS 30 com Vitamina E 1Kg - Sunlau</t>
+          <t>Capa de Chuva Policap PVC Forrado Azul (Tamanho: M)</t>
         </is>
       </c>
       <c r="J65" s="6" t="n">
-        <v>112.96</v>
+        <v>36.99</v>
       </c>
       <c r="K65" s="2" t="n"/>
-      <c r="L65" s="2" t="n"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>Costura 'por solda eletrônica' aceita como costura selada; equivalência não confirmada pelo fabricante (decisão de 13/10/2026).</t>
+        </is>
+      </c>
       <c r="M65" s="6" t="n">
-        <v>112.96</v>
+        <v>36.99</v>
       </c>
       <c r="N65" s="6" t="n">
-        <v>21.9</v>
+        <v>20.44</v>
       </c>
       <c r="O65" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 31,27 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 21,90 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,44 7 dias úteis PAC</t>
         </is>
       </c>
       <c r="P65" s="2" t="n"/>
@@ -4531,17 +4573,17 @@
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1117</t>
         </is>
       </c>
       <c r="C66" s="3" t="inlineStr">
         <is>
-          <t>BLOQUEADOR/PROTETOR SOLAR FPS 30 OU 50 - PARA SERVIÇOS EXTERNOS; MANTER COMO ITEM DE PROTEÇÃO OCUPACIONAL NA COMPOSIÇÃO.</t>
+          <t>CAPA DE CHUVA - PVC IMPERMEÁVEL, COM CAPUZ E COSTURAS SELADAS.</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E66" s="4" t="n">
@@ -4549,41 +4591,35 @@
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
-          <t>SEGURANCA TOTAL EPIS LTDA</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>39.268.527/0001-37</t>
-        </is>
-      </c>
-      <c r="H66" s="5" t="inlineStr">
-        <is>
-          <t>https://www.segurancatotal.com.br/protetor-solar-30-fps-com-repelente-120gr</t>
-        </is>
-      </c>
+          <t>46.412.993/0001-00</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="n"/>
       <c r="I66" s="3" t="inlineStr">
         <is>
-          <t>Protetor Solar 30 FPS Com Repelente Mavaro 120G</t>
-        </is>
-      </c>
-      <c r="J66" s="6" t="n">
-        <v>32.41</v>
-      </c>
+          <t>CAPA P/ CHUVA PVC MORCEGO C/CAPUZ GRANDE AMARELA</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="n"/>
       <c r="K66" s="2" t="n"/>
       <c r="L66" s="2" t="n"/>
-      <c r="M66" s="6" t="n">
-        <v>32.41</v>
-      </c>
-      <c r="N66" s="6" t="n">
-        <v>18.4</v>
-      </c>
+      <c r="M66" s="2" t="n"/>
+      <c r="N66" s="2" t="n"/>
       <c r="O66" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
-        </is>
-      </c>
-      <c r="P66" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P66" s="5" t="inlineStr">
+        <is>
+          <t>https://www.supriflex.com.br/produto/capa-pvc-morcego-ccapuz-grande-amarela.html</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -4593,17 +4629,17 @@
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="C67" s="3" t="inlineStr">
         <is>
-          <t>BLOQUEADOR/PROTETOR SOLAR FPS 30 OU 50 - PARA SERVIÇOS EXTERNOS; MANTER COMO ITEM DE PROTEÇÃO OCUPACIONAL NA COMPOSIÇÃO.</t>
+          <t>BONÉ ÁRABE/SOMBREIRO PARA PROTEÇÃO SOLAR - PARA SERVIÇOS EXTERNOS.</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E67" s="4" t="n">
@@ -4611,38 +4647,38 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>ASTRO DISTRIBUIDORA LTDA</t>
+          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>18.597.685/0001-60</t>
+          <t>20.838.307/0001-73</t>
         </is>
       </c>
       <c r="H67" s="5" t="inlineStr">
         <is>
-          <t>https://www.astrodistribuidora.com/bloqueador-solar-fps-30-120g-camper</t>
+          <t>https://www.lojadoepi.com.br/bone-arabe-helanca-azul-ca-39856-pr-22257-ca-39856-p4964</t>
         </is>
       </c>
       <c r="I67" s="3" t="inlineStr">
         <is>
-          <t>Bloqueador Solar FPS 30 120g - Camper</t>
+          <t>Bone Arabe Helanca Azul Ca 39856</t>
         </is>
       </c>
       <c r="J67" s="6" t="n">
-        <v>2.04</v>
+        <v>11.47</v>
       </c>
       <c r="K67" s="2" t="n"/>
       <c r="L67" s="2" t="n"/>
       <c r="M67" s="6" t="n">
-        <v>2.04</v>
+        <v>11.47</v>
       </c>
       <c r="N67" s="6" t="n">
-        <v>26.82</v>
+        <v>21.39</v>
       </c>
       <c r="O67" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: JADLOG - Entrega em até 5 dias úteis - R$26,82 BRASPRESS - Entrega em até 15 dias úteis - R$34,70</t>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 21,39 7 dia(s) útil(eis)</t>
         </is>
       </c>
       <c r="P67" s="2" t="n"/>
@@ -4655,75 +4691,567 @@
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1118</t>
         </is>
       </c>
       <c r="C68" s="3" t="inlineStr">
         <is>
-          <t>BLOQUEADOR/PROTETOR SOLAR FPS 30 OU 50 - PARA SERVIÇOS EXTERNOS; MANTER COMO ITEM DE PROTEÇÃO OCUPACIONAL NA COMPOSIÇÃO.</t>
+          <t>BONÉ ÁRABE/SOMBREIRO PARA PROTEÇÃO SOLAR - PARA SERVIÇOS EXTERNOS.</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E68" s="4" t="n">
-        <v>46306</v>
+        <v>46308</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>Gimba</t>
+          <t>TR Distribuidora de Equipamentos de Segurança LTDA</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>54.651.716/0011-50</t>
+          <t>14.213.841/0001-91</t>
         </is>
       </c>
       <c r="H68" s="5" t="inlineStr">
         <is>
-          <t>https://www.gimba.com.br/protetor-solar/protetor-solar-sunlau-fps-30-120g-1-un/?PID=134621</t>
+          <t>https://www.trepis.com.br/bone-arabe-em-brim-com-velcro-para-protecao-solar-azul-ca-49731</t>
         </is>
       </c>
       <c r="I68" s="3" t="inlineStr">
         <is>
-          <t>Protetor Solar Sunlau FPS 30 120G 1 UN</t>
+          <t>Boné Árabe em Brim com Velcro para Proteção Solar Azul C.A. 49731</t>
         </is>
       </c>
       <c r="J68" s="6" t="n">
-        <v>18.99</v>
+        <v>18.38</v>
       </c>
       <c r="K68" s="2" t="n"/>
       <c r="L68" s="2" t="n"/>
       <c r="M68" s="6" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="N68" s="6" t="n">
+        <v>21.55</v>
+      </c>
+      <c r="O68" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: PAC R$ 27,59 7 dias úteis. JADLOG .Package R$ 21,55 Capital de todo Brasil: 01 a 03 dias. Interior de Todo Brasil: 02 a 05 dias. JADLOG Econômico R$ 7</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="n"/>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>1118</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>BONÉ ÁRABE/SOMBREIRO PARA PROTEÇÃO SOLAR - PARA SERVIÇOS EXTERNOS.</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>Fermarcs Ferramentas</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>08.615.223/0001-75</t>
+        </is>
+      </c>
+      <c r="H69" s="5" t="inlineStr">
+        <is>
+          <t>https://www.fermarcsferramentas.com.br/equipamentos-de-protecao/acessorios-para-cabeca/bone-arabe-poliester-stela</t>
+        </is>
+      </c>
+      <c r="I69" s="3" t="inlineStr">
+        <is>
+          <t>Bone Arabe Poliester S/Tela</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="K69" s="2" t="n"/>
+      <c r="L69" s="2" t="n"/>
+      <c r="M69" s="6" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="N69" s="2" t="n"/>
+      <c r="O69" s="3" t="inlineStr">
+        <is>
+          <t>Frete não calculado (GO para GO)</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="n"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>1118</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>BONÉ ÁRABE/SOMBREIRO PARA PROTEÇÃO SOLAR - PARA SERVIÇOS EXTERNOS.</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>A Master EPI</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>16.603.654/0001-40</t>
+        </is>
+      </c>
+      <c r="H70" s="5" t="inlineStr">
+        <is>
+          <t>https://www.amasterepi.com.br/19167/bone-arabe-azul-helanca-c-protecao-pescoco-prime</t>
+        </is>
+      </c>
+      <c r="I70" s="3" t="inlineStr">
+        <is>
+          <t>Bone Arabe Azul Helanca C/ Protecao Pescoço Prime</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="K70" s="2" t="n"/>
+      <c r="L70" s="2" t="n"/>
+      <c r="M70" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="N70" s="6" t="n">
+        <v>32.85</v>
+      </c>
+      <c r="O70" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Entrega Econômica R$ 32,85 De 6 A 7 dia(s) Úteis</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="n"/>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>1118</t>
+        </is>
+      </c>
+      <c r="C71" s="3" t="inlineStr">
+        <is>
+          <t>BONÉ ÁRABE/SOMBREIRO PARA PROTEÇÃO SOLAR - PARA SERVIÇOS EXTERNOS.</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>ZEUS DO BRASIL</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>82.699.588/0001-88</t>
+        </is>
+      </c>
+      <c r="H71" s="5" t="inlineStr">
+        <is>
+          <t>https://www.shoppingdaseguranca.com.br/touca-arabe-helanca-cinza-bone</t>
+        </is>
+      </c>
+      <c r="I71" s="3" t="inlineStr">
+        <is>
+          <t>Touca Árabe Tipo Boné em Helanca Cinza</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="K71" s="2" t="n"/>
+      <c r="L71" s="2" t="n"/>
+      <c r="M71" s="6" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="N71" s="6" t="n">
+        <v>61.87</v>
+      </c>
+      <c r="O71" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: Entrega Econômica 8 dias úteis R$ 61,87</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="n"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="C72" s="3" t="inlineStr">
+        <is>
+          <t>BLOQUEADOR/PROTETOR SOLAR FPS 30 OU 50 - PARA SERVIÇOS EXTERNOS; MANTER COMO ITEM DE PROTEÇÃO OCUPACIONAL NA COMPOSIÇÃO.</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>31.893.116/0001-20</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>https://www.loja.bhzepi.com.br/protetor-solar-sunlau-30-fps-de-1kg</t>
+        </is>
+      </c>
+      <c r="I72" s="3" t="inlineStr">
+        <is>
+          <t>PROTETOR SOLAR PARA PRAIA SUNLAU 30 FPS DE 1KG</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="K72" s="2" t="n"/>
+      <c r="L72" s="2" t="n"/>
+      <c r="M72" s="6" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="N72" s="2" t="n"/>
+      <c r="O72" s="3" t="inlineStr">
+        <is>
+          <t>Frete grátis para o CEP 74933-130</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="n"/>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="C73" s="3" t="inlineStr">
+        <is>
+          <t>BLOQUEADOR/PROTETOR SOLAR FPS 30 OU 50 - PARA SERVIÇOS EXTERNOS; MANTER COMO ITEM DE PROTEÇÃO OCUPACIONAL NA COMPOSIÇÃO.</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>27.061.442/0002-85</t>
+        </is>
+      </c>
+      <c r="H73" s="5" t="inlineStr">
+        <is>
+          <t>https://www.lojas360.com.br/protecao-solar/protetor-solar-fps-30-com-vitamina-e-1kg</t>
+        </is>
+      </c>
+      <c r="I73" s="3" t="inlineStr">
+        <is>
+          <t>Protetor Solar FPS 30 com Vitamina E 1Kg - Sunlau</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="n">
+        <v>112.96</v>
+      </c>
+      <c r="K73" s="2" t="n"/>
+      <c r="L73" s="2" t="n"/>
+      <c r="M73" s="6" t="n">
+        <v>112.96</v>
+      </c>
+      <c r="N73" s="6" t="n">
+        <v>21.9</v>
+      </c>
+      <c r="O73" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 31,27 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 21,90 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="n"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="C74" s="3" t="inlineStr">
+        <is>
+          <t>BLOQUEADOR/PROTETOR SOLAR FPS 30 OU 50 - PARA SERVIÇOS EXTERNOS; MANTER COMO ITEM DE PROTEÇÃO OCUPACIONAL NA COMPOSIÇÃO.</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>39.268.527/0001-37</t>
+        </is>
+      </c>
+      <c r="H74" s="5" t="inlineStr">
+        <is>
+          <t>https://www.segurancatotal.com.br/protetor-solar-30-fps-com-repelente-120gr</t>
+        </is>
+      </c>
+      <c r="I74" s="3" t="inlineStr">
+        <is>
+          <t>Protetor Solar 30 FPS Com Repelente Mavaro 120G</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="K74" s="2" t="n"/>
+      <c r="L74" s="2" t="n"/>
+      <c r="M74" s="6" t="n">
+        <v>32.41</v>
+      </c>
+      <c r="N74" s="6" t="n">
+        <v>18.4</v>
+      </c>
+      <c r="O74" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="n"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="C75" s="3" t="inlineStr">
+        <is>
+          <t>BLOQUEADOR/PROTETOR SOLAR FPS 30 OU 50 - PARA SERVIÇOS EXTERNOS; MANTER COMO ITEM DE PROTEÇÃO OCUPACIONAL NA COMPOSIÇÃO.</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>ASTRO DISTRIBUIDORA LTDA</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>18.597.685/0001-60</t>
+        </is>
+      </c>
+      <c r="H75" s="5" t="inlineStr">
+        <is>
+          <t>https://www.astrodistribuidora.com/bloqueador-solar-fps-30-120g-camper</t>
+        </is>
+      </c>
+      <c r="I75" s="3" t="inlineStr">
+        <is>
+          <t>Bloqueador Solar FPS 30 120g - Camper</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="K75" s="2" t="n"/>
+      <c r="L75" s="2" t="n"/>
+      <c r="M75" s="6" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="N75" s="6" t="n">
+        <v>26.82</v>
+      </c>
+      <c r="O75" s="3" t="inlineStr">
+        <is>
+          <t>Opção mais barata para o CEP 74933-130: JADLOG - Entrega em até 5 dias úteis - R$26,82 BRASPRESS - Entrega em até 15 dias úteis - R$34,70</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="n"/>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>EPI / UNIFORME</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>1119</t>
+        </is>
+      </c>
+      <c r="C76" s="3" t="inlineStr">
+        <is>
+          <t>BLOQUEADOR/PROTETOR SOLAR FPS 30 OU 50 - PARA SERVIÇOS EXTERNOS; MANTER COMO ITEM DE PROTEÇÃO OCUPACIONAL NA COMPOSIÇÃO.</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>Gimba</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>54.651.716/0011-50</t>
+        </is>
+      </c>
+      <c r="H76" s="5" t="inlineStr">
+        <is>
+          <t>https://www.gimba.com.br/protetor-solar/protetor-solar-sunlau-fps-30-120g-1-un/?PID=134621</t>
+        </is>
+      </c>
+      <c r="I76" s="3" t="inlineStr">
+        <is>
+          <t>Protetor Solar Sunlau FPS 30 120G 1 UN</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="n">
         <v>18.99</v>
       </c>
-      <c r="N68" s="6" t="n">
+      <c r="K76" s="2" t="n"/>
+      <c r="L76" s="2" t="n"/>
+      <c r="M76" s="6" t="n">
+        <v>18.99</v>
+      </c>
+      <c r="N76" s="6" t="n">
         <v>30.32</v>
       </c>
-      <c r="O68" s="3" t="inlineStr">
+      <c r="O76" s="3" t="inlineStr">
         <is>
           <t>Opção mais barata para o CEP 74933-130: Envio: Correios - PAC Valor: R$ 30,32</t>
         </is>
       </c>
-      <c r="P68" s="2" t="n"/>
+      <c r="P76" s="2" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P68"/>
+  <autoFilter ref="A1:P76"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H3" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H4" r:id="rId3"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H7" r:id="rId6"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H8" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H11" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId12"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
@@ -4748,11 +5276,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H35" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H36" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H37" r:id="rId36"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H38" r:id="rId37"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId41"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId44"/>
@@ -4762,23 +5290,31 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H49" r:id="rId48"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H50" r:id="rId49"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H51" r:id="rId50"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P52" r:id="rId51"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P53" r:id="rId52"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H54" r:id="rId53"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H55" r:id="rId54"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H56" r:id="rId55"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H57" r:id="rId56"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P58" r:id="rId57"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H59" r:id="rId58"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P60" r:id="rId59"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H61" r:id="rId60"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H62" r:id="rId61"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H63" r:id="rId62"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H64" r:id="rId63"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H65" r:id="rId64"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P66" r:id="rId65"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H67" r:id="rId66"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H76" r:id="rId75"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/FNDE/Centro Oeste/Entrega/EPI UNIFORME/fnde_resultado_merge.xlsx
+++ b/FNDE/Centro Oeste/Entrega/EPI UNIFORME/fnde_resultado_merge.xlsx
@@ -1191,46 +1191,44 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Multiseg Comercio de Equipamentos de Seguranca Ltda</t>
+          <t>Mais Segurança EPI</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10.498.304/0001-84</t>
+          <t>43.903.641/0001-69</t>
         </is>
       </c>
       <c r="H12" s="5" t="inlineStr">
         <is>
-          <t>https://www.multiseg.com.br/4458/tenis-de-segurana-antiderrapante-sticky-shoe-copa-branco-ca-44589</t>
+          <t>https://maisseguranca.online/#/produto-detalhes/nUNEWOBUivWtuxf5g7uS3ulpNCn2/-N4ce5UWWtjnB32sQoGd</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>Tênis de Segurança Sticky Shoe Copa Branco Ca 44589 Antiderrapante</t>
+          <t>SAPATO IMPERMEAVEL ANTIDERRAPANTE PRETO MAN 41 - STICKY SHOES CA.39674</t>
         </is>
       </c>
       <c r="J12" s="6" t="n">
-        <v>89.59999999999999</v>
+        <v>78</v>
       </c>
       <c r="K12" s="2" t="n"/>
       <c r="L12" s="2" t="n"/>
       <c r="M12" s="6" t="n">
-        <v>89.59999999999999</v>
-      </c>
-      <c r="N12" s="6" t="n">
-        <v>32.85</v>
-      </c>
+        <v>78</v>
+      </c>
+      <c r="N12" s="2" t="n"/>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Pac R$ 32,85 De 9 A 10 dia(s) Úteis</t>
+          <t>Frete não calculado (GO para GO)</t>
         </is>
       </c>
       <c r="P12" s="2" t="n"/>
@@ -1253,39 +1251,49 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
-        <v>46308</v>
+        <v>46307</v>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>A MASTER ARTIGOS PARA PROTECAO INDIVIDUAL E INDUSTRIAL LTDA (A Master EPI)</t>
+          <t>Multiseg Comercio de Equipamentos de Seguranca Ltda</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>16.603.654/0001-40</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="n"/>
-      <c r="I13" s="3" t="n"/>
-      <c r="J13" s="2" t="n"/>
+          <t>10.498.304/0001-84</t>
+        </is>
+      </c>
+      <c r="H13" s="5" t="inlineStr">
+        <is>
+          <t>https://www.multiseg.com.br/4458/tenis-de-segurana-antiderrapante-sticky-shoe-copa-branco-ca-44589</t>
+        </is>
+      </c>
+      <c r="I13" s="3" t="inlineStr">
+        <is>
+          <t>Tênis de Segurança Sticky Shoe Copa Branco Ca 44589 Antiderrapante</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>89.59999999999999</v>
+      </c>
       <c r="K13" s="2" t="n"/>
       <c r="L13" s="2" t="n"/>
-      <c r="M13" s="2" t="n"/>
-      <c r="N13" s="2" t="n"/>
+      <c r="M13" s="6" t="n">
+        <v>89.59999999999999</v>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>32.85</v>
+      </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="inlineStr">
-        <is>
-          <t>https://www.amasterepi.com.br/busca?q=Cal%C3%A7ado%20De%20Seguran%C3%A7a%20Antiderrapante</t>
-        </is>
-      </c>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 32,85 De 9 A 10 dia(s) Úteis</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1295,17 +1303,17 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>1108</t>
+          <t>1107</t>
         </is>
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>BOTA DE PVC/BORRACHA - IMPERMEÁVEL, SOLADO ANTIDERRAPANTE, CANO MÉDIO OU LONGO.</t>
+          <t>CALÇADO DE SEGURANÇA ANTIDERRAPANTE - PROTEÇÃO CONTRA AGENTES MECÂNICOS; IMPERMEÁVEL QUANDO APLICÁVEL.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
@@ -1313,45 +1321,31 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+          <t>A MASTER ARTIGOS PARA PROTECAO INDIVIDUAL E INDUSTRIAL LTDA (A Master EPI)</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>27.061.442/0002-85</t>
-        </is>
-      </c>
-      <c r="H14" s="5" t="inlineStr">
-        <is>
-          <t>https://www.lojas360.com.br/bicodepvc/bota-de-pvc-cano-longo-preta-com-forro-biqueira-composite?variant_id=5711</t>
-        </is>
-      </c>
-      <c r="I14" s="3" t="inlineStr">
-        <is>
-          <t>Bota de Pvc Cano Longo Preta Com Forro Biqueira Composite</t>
-        </is>
-      </c>
-      <c r="J14" s="6" t="n">
-        <v>176.61</v>
-      </c>
+          <t>16.603.654/0001-40</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="n"/>
+      <c r="I14" s="3" t="n"/>
+      <c r="J14" s="2" t="n"/>
       <c r="K14" s="2" t="n"/>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>PVC aceito como impermeável (equivalência).</t>
-        </is>
-      </c>
-      <c r="M14" s="6" t="n">
-        <v>176.61</v>
-      </c>
-      <c r="N14" s="6" t="n">
-        <v>1687.82</v>
-      </c>
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="n"/>
+      <c r="N14" s="2" t="n"/>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Frete Valor Prazo de Entrega e Observações: Logística Própria FAVORITA R$ 1.687,82 Até 5 a 6 dia(s) úteis após o faturamento do pedido FRETE GRÁTIS PA</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="inlineStr">
+        <is>
+          <t>https://www.amasterepi.com.br/busca?q=Cal%C3%A7ado%20De%20Seguran%C3%A7a%20Antiderrapante</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1379,42 +1373,42 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>SEGURANCA TOTAL EPIS LTDA</t>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>39.268.527/0001-37</t>
+          <t>27.061.442/0002-85</t>
         </is>
       </c>
       <c r="H15" s="5" t="inlineStr">
         <is>
-          <t>https://www.segurancatotal.com.br/bota-pvc-impermeavel-branco</t>
+          <t>https://www.lojas360.com.br/bicodepvc/bota-de-pvc-cano-longo-preta-com-forro-biqueira-composite?variant_id=5711</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t>Bota PVC Impermeável Innpro Cano Médio Branco CA 36025 (numeração innpro: 34/35)</t>
+          <t>Bota de Pvc Cano Longo Preta Com Forro Biqueira Composite</t>
         </is>
       </c>
       <c r="J15" s="6" t="n">
-        <v>55.05</v>
+        <v>176.61</v>
       </c>
       <c r="K15" s="2" t="n"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: solado antiderrapante.</t>
+          <t>PVC aceito como impermeável (equivalência).</t>
         </is>
       </c>
       <c r="M15" s="6" t="n">
-        <v>55.05</v>
+        <v>176.61</v>
       </c>
       <c r="N15" s="6" t="n">
-        <v>18.4</v>
+        <v>1687.82</v>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
+          <t>Opção mais barata para o CEP 74933-130: Frete Valor Prazo de Entrega e Observações: Logística Própria FAVORITA R$ 1.687,82 Até 5 a 6 dia(s) úteis após o faturamento do pedido FRETE GRÁTIS PA</t>
         </is>
       </c>
       <c r="P15" s="2" t="n"/>
@@ -1437,7 +1431,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E16" s="4" t="n">
@@ -1445,40 +1439,42 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Casa do Pica-Pau Ltda</t>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>50.223.823/0001-54</t>
+          <t>39.268.527/0001-37</t>
         </is>
       </c>
       <c r="H16" s="5" t="inlineStr">
         <is>
-          <t>https://www.casadopicapau.com.br/bota-galocha-baspan-ultraleve-pvc-cano-longo-azul-amarelo-nautica/p</t>
+          <t>https://www.segurancatotal.com.br/bota-pvc-impermeavel-branco</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t>Bota Galocha Baspan Ultraleve de PVC Cano Longo</t>
+          <t>Bota PVC Impermeável Innpro Cano Médio Branco CA 36025 (numeração innpro: 34/35)</t>
         </is>
       </c>
       <c r="J16" s="6" t="n">
-        <v>60.41</v>
+        <v>55.05</v>
       </c>
       <c r="K16" s="2" t="n"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>PVC aceito como impermeável (equivalência).</t>
+          <t>Característica não confirmada na página do produto: solado antiderrapante.</t>
         </is>
       </c>
       <c r="M16" s="6" t="n">
-        <v>60.41</v>
-      </c>
-      <c r="N16" s="2" t="n"/>
+        <v>55.05</v>
+      </c>
+      <c r="N16" s="6" t="n">
+        <v>18.4</v>
+      </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO) | frete real: R$ 18,70</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P16" s="2" t="n"/>
@@ -1501,7 +1497,7 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E17" s="4" t="n">
@@ -1509,26 +1505,26 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
+          <t>Casa do Pica-Pau Ltda</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>20.838.307/0001-73</t>
+          <t>50.223.823/0001-54</t>
         </is>
       </c>
       <c r="H17" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojadoepi.com.br/bota-de-pvc-work-cano-medio-cor-preta-comprimento-28-cm-ca-36025-innpro-p3301?pp=/40.1438/</t>
+          <t>https://www.casadopicapau.com.br/bota-galocha-baspan-ultraleve-pvc-cano-longo-azul-amarelo-nautica/p</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t>Bota de PVC Work Cano Médio Cor Preta Comprimento 28 cm CA 36025 INNPRO</t>
+          <t>Bota Galocha Baspan Ultraleve de PVC Cano Longo</t>
         </is>
       </c>
       <c r="J17" s="6" t="n">
-        <v>44.56</v>
+        <v>60.41</v>
       </c>
       <c r="K17" s="2" t="n"/>
       <c r="L17" s="2" t="inlineStr">
@@ -1537,14 +1533,12 @@
         </is>
       </c>
       <c r="M17" s="6" t="n">
-        <v>44.56</v>
-      </c>
-      <c r="N17" s="6" t="n">
-        <v>25.47</v>
-      </c>
+        <v>60.41</v>
+      </c>
+      <c r="N17" s="2" t="n"/>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Pac R$ 25,47 7 dia(s) útil(eis)</t>
+          <t>Frete não calculado (GO para GO) | frete real: R$ 18,70</t>
         </is>
       </c>
       <c r="P17" s="2" t="n"/>
@@ -1567,50 +1561,50 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>MS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Panan</t>
+          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>15.448.996/0001-70</t>
+          <t>20.838.307/0001-73</t>
         </is>
       </c>
       <c r="H18" s="5" t="inlineStr">
         <is>
-          <t>https://www.panan.com.br/pecas-e-epis/calcados/bota-pvc-cano-longo-n-41-bpcl11-vulcabras</t>
+          <t>https://www.lojadoepi.com.br/bota-de-pvc-work-cano-medio-cor-preta-comprimento-28-cm-ca-36025-innpro-p3301?pp=/40.1438/</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t>Bota PVC Cano Longo N° 41 BPCL11 - Vulcabras</t>
+          <t>Bota de PVC Work Cano Médio Cor Preta Comprimento 28 cm CA 36025 INNPRO</t>
         </is>
       </c>
       <c r="J18" s="6" t="n">
-        <v>86.90000000000001</v>
+        <v>44.56</v>
       </c>
       <c r="K18" s="2" t="n"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>PVC aceito como impermeável (equivalência). Característica não confirmada na página do produto: solado antiderrapante.</t>
+          <t>PVC aceito como impermeável (equivalência).</t>
         </is>
       </c>
       <c r="M18" s="6" t="n">
-        <v>86.90000000000001</v>
+        <v>44.56</v>
       </c>
       <c r="N18" s="6" t="n">
-        <v>38.7</v>
+        <v>25.47</v>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Correios Econômico R$ 38,70 7 a 9 dias úteis</t>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 25,47 7 dia(s) útil(eis)</t>
         </is>
       </c>
       <c r="P18" s="2" t="n"/>
@@ -1623,56 +1617,60 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1108</t>
         </is>
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>LUVA DE PVC - CANO MÉDIO OU LONGO; PARA ATIVIDADES DE LIMPEZA.</t>
+          <t>BOTA DE PVC/BORRACHA - IMPERMEÁVEL, SOLADO ANTIDERRAPANTE, CANO MÉDIO OU LONGO.</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MS</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+          <t>Panan</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>27.061.442/0002-85</t>
+          <t>15.448.996/0001-70</t>
         </is>
       </c>
       <c r="H19" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojas360.com.br/luvas-de-seguranca/luva-de-pvc-sem-forro-palma-aspera-70cm-com-ombreira</t>
+          <t>https://www.panan.com.br/pecas-e-epis/calcados/bota-pvc-cano-longo-n-41-bpcl11-vulcabras</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t>Luva de PVC Sem Forro Palma Áspera 70cm Com Ombreira</t>
+          <t>Bota PVC Cano Longo N° 41 BPCL11 - Vulcabras</t>
         </is>
       </c>
       <c r="J19" s="6" t="n">
-        <v>52.44</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="K19" s="2" t="n"/>
-      <c r="L19" s="2" t="n"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>PVC aceito como impermeável (equivalência). Característica não confirmada na página do produto: solado antiderrapante.</t>
+        </is>
+      </c>
       <c r="M19" s="6" t="n">
-        <v>52.44</v>
+        <v>86.90000000000001</v>
       </c>
       <c r="N19" s="6" t="n">
-        <v>18.4</v>
+        <v>38.7</v>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
+          <t>Opção mais barata para o CEP 74933-130: Correios Econômico R$ 38,70 7 a 9 dias úteis</t>
         </is>
       </c>
       <c r="P19" s="2" t="n"/>
@@ -1703,38 +1701,38 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>20.838.307/0001-73</t>
+          <t>27.061.442/0002-85</t>
         </is>
       </c>
       <c r="H20" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojadoepi.com.br/luva-de-pvc-para-jatista-ca-43248-ldi-safety-107-p2283</t>
+          <t>https://www.lojas360.com.br/luvas-de-seguranca/luva-de-pvc-sem-forro-palma-aspera-70cm-com-ombreira</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t>Luva de PVC para Jatista CA 43248 LDI Safety</t>
+          <t>Luva de PVC Sem Forro Palma Áspera 70cm Com Ombreira</t>
         </is>
       </c>
       <c r="J20" s="6" t="n">
-        <v>65.88</v>
+        <v>52.44</v>
       </c>
       <c r="K20" s="2" t="n"/>
       <c r="L20" s="2" t="n"/>
       <c r="M20" s="6" t="n">
-        <v>65.88</v>
+        <v>52.44</v>
       </c>
       <c r="N20" s="6" t="n">
-        <v>27.98</v>
+        <v>18.4</v>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Pac R$ 27,98 7 dia(s) útil(eis)</t>
+          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
         </is>
       </c>
       <c r="P20" s="2" t="n"/>
@@ -1757,44 +1755,46 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E21" s="4" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Goiás Ferramentas</t>
+          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>09.497.806/0001-01</t>
+          <t>20.838.307/0001-73</t>
         </is>
       </c>
       <c r="H21" s="5" t="inlineStr">
         <is>
-          <t>https://www.goiasferramentas.com.br/produto/615-luva-de-pvc-cano-longo-45cm-kalipso</t>
+          <t>https://www.lojadoepi.com.br/luva-de-pvc-para-jatista-ca-43248-ldi-safety-107-p2283</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t>Luva de PVC Cano Longo 45cm Kalipso</t>
+          <t>Luva de PVC para Jatista CA 43248 LDI Safety</t>
         </is>
       </c>
       <c r="J21" s="6" t="n">
-        <v>23.33</v>
+        <v>65.88</v>
       </c>
       <c r="K21" s="2" t="n"/>
       <c r="L21" s="2" t="n"/>
       <c r="M21" s="6" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="N21" s="2" t="n"/>
+        <v>65.88</v>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>27.98</v>
+      </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO)</t>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 27,98 7 dia(s) útil(eis)</t>
         </is>
       </c>
       <c r="P21" s="2" t="n"/>
@@ -1821,35 +1821,35 @@
         </is>
       </c>
       <c r="E22" s="4" t="n">
-        <v>46306</v>
+        <v>46304</v>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Fermarcs Ferramentas</t>
+          <t>Goiás Ferramentas</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>08.615.223/0001-75</t>
+          <t>09.497.806/0001-01</t>
         </is>
       </c>
       <c r="H22" s="5" t="inlineStr">
         <is>
-          <t>https://www.fermarcsferramentas.com.br/luvas/luva-pvc-azul-s-forro-palma-lisa-35cm-ca34593</t>
+          <t>https://www.goiasferramentas.com.br/produto/615-luva-de-pvc-cano-longo-45cm-kalipso</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t>Luva Pvc Azul S/ Forro Palma Lisa 35cm Ca34593</t>
+          <t>Luva de PVC Cano Longo 45cm Kalipso</t>
         </is>
       </c>
       <c r="J22" s="6" t="n">
-        <v>24.9</v>
+        <v>23.33</v>
       </c>
       <c r="K22" s="2" t="n"/>
       <c r="L22" s="2" t="n"/>
       <c r="M22" s="6" t="n">
-        <v>24.9</v>
+        <v>23.33</v>
       </c>
       <c r="N22" s="2" t="n"/>
       <c r="O22" s="3" t="inlineStr">
@@ -1867,60 +1867,54 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>1110</t>
+          <t>1109</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>LUVA DE LÁTEX FORRADA - CANO CURTO; TAMANHOS VARIADOS.</t>
+          <t>LUVA DE PVC - CANO MÉDIO OU LONGO; PARA ATIVIDADES DE LIMPEZA.</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E23" s="4" t="n">
-        <v>46308</v>
+        <v>46306</v>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
+          <t>Fermarcs Ferramentas</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>31.893.116/0001-20</t>
+          <t>08.615.223/0001-75</t>
         </is>
       </c>
       <c r="H23" s="5" t="inlineStr">
         <is>
-          <t>https://www.loja.bhzepi.com.br/luva-latex-amarela-forrada-ca-42023-imbat</t>
+          <t>https://www.fermarcsferramentas.com.br/luvas/luva-pvc-azul-s-forro-palma-lisa-35cm-ca34593</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t>LUVA LATEX AMARELA FORRADA CA 42023 IMBAT (Tamanho: M)</t>
+          <t>Luva Pvc Azul S/ Forro Palma Lisa 35cm Ca34593</t>
         </is>
       </c>
       <c r="J23" s="6" t="n">
-        <v>5</v>
+        <v>24.9</v>
       </c>
       <c r="K23" s="2" t="n"/>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: cano curto.</t>
-        </is>
-      </c>
+      <c r="L23" s="2" t="n"/>
       <c r="M23" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="N23" s="6" t="n">
-        <v>20.62</v>
-      </c>
+        <v>24.9</v>
+      </c>
+      <c r="N23" s="2" t="n"/>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC R$ 26,55 5 dias úteis Jadlog Package R$ 40,39 3 dias úteis SEDEX</t>
+          <t>Frete não calculado (GO para GO)</t>
         </is>
       </c>
       <c r="P23" s="2" t="n"/>
@@ -1943,7 +1937,7 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E24" s="4" t="n">
@@ -1951,42 +1945,42 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>27.061.442/0002-85</t>
+          <t>31.893.116/0001-20</t>
         </is>
       </c>
       <c r="H24" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojas360.com.br/luvas-de-seguranca/luva-latex-antiderrapante-orange-kalipso-c-a-32499?variant_id=4253</t>
+          <t>https://www.loja.bhzepi.com.br/luva-latex-amarela-forrada-ca-42023-imbat</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t>Luva Látex Antiderrapante Orange Kalipso | C.A. 32499</t>
+          <t>LUVA LATEX AMARELA FORRADA CA 42023 IMBAT (Tamanho: M)</t>
         </is>
       </c>
       <c r="J24" s="6" t="n">
-        <v>12.26</v>
+        <v>5</v>
       </c>
       <c r="K24" s="2" t="n"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: forrada, cano curto.</t>
+          <t>Característica não confirmada na página do produto: cano curto.</t>
         </is>
       </c>
       <c r="M24" s="6" t="n">
-        <v>12.26</v>
+        <v>5</v>
       </c>
       <c r="N24" s="6" t="n">
-        <v>18.4</v>
+        <v>20.62</v>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC R$ 26,55 5 dias úteis Jadlog Package R$ 40,39 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P24" s="2" t="n"/>
@@ -2009,7 +2003,7 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E25" s="4" t="n">
@@ -2017,42 +2011,42 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
+          <t>27.061.442/0002-85</t>
         </is>
       </c>
       <c r="H25" s="5" t="inlineStr">
         <is>
-          <t>https://www.supriflex.com.br/produto/luva-latex-multiuso-quality-forte-vabene-verde-p.html</t>
+          <t>https://www.lojas360.com.br/luvas-de-seguranca/luva-latex-antiderrapante-orange-kalipso-c-a-32499?variant_id=4253</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>Luva Látex Multiuso Quality Forte Vabene Verde P</t>
+          <t>Luva Látex Antiderrapante Orange Kalipso | C.A. 32499</t>
         </is>
       </c>
       <c r="J25" s="6" t="n">
-        <v>4.99</v>
+        <v>12.26</v>
       </c>
       <c r="K25" s="2" t="n"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>Característica não confirmada na página do produto: cano curto.</t>
+          <t>Característica não confirmada na página do produto: forrada, cano curto.</t>
         </is>
       </c>
       <c r="M25" s="6" t="n">
-        <v>4.99</v>
+        <v>12.26</v>
       </c>
       <c r="N25" s="6" t="n">
-        <v>28.06</v>
+        <v>18.4</v>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 28,06 11 dias úteis Correios - Mini Envios R$ 31,54 7 dias úteis Correios PAC R$ 32,18 7 dias úteis Jadlog - .Package</t>
+          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
         </is>
       </c>
       <c r="P25" s="2" t="n"/>
@@ -2075,36 +2069,34 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>14/10/2026</t>
-        </is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>46308</v>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>SEGURANCA TOTAL EPIS LTDA</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>39.268.527/0001-37</t>
+          <t>46.412.993/0001-00</t>
         </is>
       </c>
       <c r="H26" s="5" t="inlineStr">
         <is>
-          <t>https://www.segurancatotal.com.br/luva-de-latex-kalipso-amarela-ca-13959</t>
+          <t>https://www.supriflex.com.br/produto/luva-latex-multiuso-quality-forte-vabene-verde-p.html</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t>Luva de Látex Multiuso Kalipso Amarela CA13959 (Tamanho: P)</t>
+          <t>Luva Látex Multiuso Quality Forte Vabene Verde P</t>
         </is>
       </c>
       <c r="J26" s="6" t="n">
-        <v>4.69</v>
+        <v>4.99</v>
       </c>
       <c r="K26" s="2" t="n"/>
       <c r="L26" s="2" t="inlineStr">
@@ -2113,14 +2105,14 @@
         </is>
       </c>
       <c r="M26" s="6" t="n">
-        <v>4.69</v>
+        <v>4.99</v>
       </c>
       <c r="N26" s="6" t="n">
-        <v>18.4</v>
+        <v>28.06</v>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 28,06 11 dias úteis Correios - Mini Envios R$ 31,54 7 dias úteis Correios PAC R$ 32,18 7 dias úteis Jadlog - .Package</t>
         </is>
       </c>
       <c r="P26" s="2" t="n"/>
@@ -2143,34 +2135,36 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>46304</v>
+          <t>SP</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>Multiseg Comercio de Equipamentos de Seguranca Ltda</t>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>10.498.304/0001-84</t>
+          <t>39.268.527/0001-37</t>
         </is>
       </c>
       <c r="H27" s="5" t="inlineStr">
         <is>
-          <t>https://www.multiseg.com.br/1619/luva-ltex-neoprene-supermix-super-safety</t>
+          <t>https://www.segurancatotal.com.br/luva-de-latex-kalipso-amarela-ca-13959</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t>Luva de Látex e Neoprene Super MIX Forrada Super Safety Bicolor - Ca 33333</t>
+          <t>Luva de Látex Multiuso Kalipso Amarela CA13959 (Tamanho: P)</t>
         </is>
       </c>
       <c r="J27" s="6" t="n">
-        <v>9.98</v>
+        <v>4.69</v>
       </c>
       <c r="K27" s="2" t="n"/>
       <c r="L27" s="2" t="inlineStr">
@@ -2179,14 +2173,14 @@
         </is>
       </c>
       <c r="M27" s="6" t="n">
-        <v>9.98</v>
+        <v>4.69</v>
       </c>
       <c r="N27" s="6" t="n">
-        <v>32.85</v>
+        <v>18.4</v>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Pac R$ 32,85 De 9 A 10 dia(s) Úteis</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC</t>
         </is>
       </c>
       <c r="P27" s="2" t="n"/>
@@ -2199,56 +2193,60 @@
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>1111</t>
+          <t>1110</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t>LUVA DE NEOPRENE - TAMANHOS VARIADOS; PARA MANIPULAÇÃO COMPATÍVEL DE PRODUTOS QUÍMICOS.</t>
+          <t>LUVA DE LÁTEX FORRADA - CANO CURTO; TAMANHOS VARIADOS.</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E28" s="4" t="n">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
+          <t>Multiseg Comercio de Equipamentos de Seguranca Ltda</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>31.893.116/0001-20</t>
+          <t>10.498.304/0001-84</t>
         </is>
       </c>
       <c r="H28" s="5" t="inlineStr">
         <is>
-          <t>https://www.loja.bhzepi.com.br/luva-latex-neoprene-bicolor-ca16779-volk</t>
+          <t>https://www.multiseg.com.br/1619/luva-ltex-neoprene-supermix-super-safety</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>LUVA LATEX NEOPRENE BICOLOR CA16779 VOLK (Tamanho: M)</t>
+          <t>Luva de Látex e Neoprene Super MIX Forrada Super Safety Bicolor - Ca 33333</t>
         </is>
       </c>
       <c r="J28" s="6" t="n">
-        <v>13</v>
+        <v>9.98</v>
       </c>
       <c r="K28" s="2" t="n"/>
-      <c r="L28" s="2" t="n"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: cano curto.</t>
+        </is>
+      </c>
       <c r="M28" s="6" t="n">
-        <v>13</v>
+        <v>9.98</v>
       </c>
       <c r="N28" s="6" t="n">
-        <v>20.62</v>
+        <v>32.85</v>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC R$ 26,55 5 dias úteis Jadlog Package R$ 40,39 3 dias úteis SEDEX</t>
+          <t>Opção mais barata para o CEP 74933-130: Pac R$ 32,85 De 9 A 10 dia(s) Úteis</t>
         </is>
       </c>
       <c r="P28" s="2" t="n"/>
@@ -2271,7 +2269,7 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E29" s="4" t="n">
@@ -2279,38 +2277,38 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>27.061.442/0002-85</t>
+          <t>31.893.116/0001-20</t>
         </is>
       </c>
       <c r="H29" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojas360.com.br/protecao-das-maos/luva-latex-neoprene-amareloazul-pl-7004-plastcor-c-a-43916?variant_id=5131</t>
+          <t>https://www.loja.bhzepi.com.br/luva-latex-neoprene-bicolor-ca16779-volk</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t>Luva Látex Neoprene Amarelo/Azul Pl 7004 Plastcor | C.A. 43916</t>
+          <t>LUVA LATEX NEOPRENE BICOLOR CA16779 VOLK (Tamanho: M)</t>
         </is>
       </c>
       <c r="J29" s="6" t="n">
-        <v>9.31</v>
+        <v>13</v>
       </c>
       <c r="K29" s="2" t="n"/>
       <c r="L29" s="2" t="n"/>
       <c r="M29" s="6" t="n">
-        <v>9.31</v>
+        <v>13</v>
       </c>
       <c r="N29" s="6" t="n">
-        <v>18.4</v>
+        <v>20.62</v>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC R$ 26,55 5 dias úteis Jadlog Package R$ 40,39 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P29" s="2" t="n"/>
@@ -2341,38 +2339,38 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>SEGURANCA TOTAL EPIS LTDA</t>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>39.268.527/0001-37</t>
+          <t>27.061.442/0002-85</t>
         </is>
       </c>
       <c r="H30" s="5" t="inlineStr">
         <is>
-          <t>https://www.segurancatotal.com.br/luva-latexneoprene-supermix-super-safety-ca-33333</t>
+          <t>https://www.lojas360.com.br/protecao-das-maos/luva-latex-neoprene-amareloazul-pl-7004-plastcor-c-a-43916?variant_id=5131</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t>Luva Látex/Neoprene Supermix Super Safety CA 33333 (Tamanho das Luvas: 7/P)</t>
+          <t>Luva Látex Neoprene Amarelo/Azul Pl 7004 Plastcor | C.A. 43916</t>
         </is>
       </c>
       <c r="J30" s="6" t="n">
-        <v>10.41</v>
+        <v>9.31</v>
       </c>
       <c r="K30" s="2" t="n"/>
       <c r="L30" s="2" t="n"/>
       <c r="M30" s="6" t="n">
-        <v>10.41</v>
+        <v>9.31</v>
       </c>
       <c r="N30" s="6" t="n">
         <v>18.4</v>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
+          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
         </is>
       </c>
       <c r="P30" s="2" t="n"/>
@@ -2395,44 +2393,46 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E31" s="4" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>Goiás Ferramentas</t>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>09.497.806/0001-01</t>
+          <t>39.268.527/0001-37</t>
         </is>
       </c>
       <c r="H31" s="5" t="inlineStr">
         <is>
-          <t>https://www.goiasferramentas.com.br/produto/13963-luva-de-latex-neoprene-kalipso-neoprex-azul-e-amarela-xg</t>
+          <t>https://www.segurancatotal.com.br/luva-latexneoprene-supermix-super-safety-ca-33333</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t>Luva de Latex / Neoprene Kalipso Neoprex Azul e Amarela XG</t>
+          <t>Luva Látex/Neoprene Supermix Super Safety CA 33333 (Tamanho das Luvas: 7/P)</t>
         </is>
       </c>
       <c r="J31" s="6" t="n">
-        <v>10.88</v>
+        <v>10.41</v>
       </c>
       <c r="K31" s="2" t="n"/>
       <c r="L31" s="2" t="n"/>
       <c r="M31" s="6" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="N31" s="2" t="n"/>
+        <v>10.41</v>
+      </c>
+      <c r="N31" s="6" t="n">
+        <v>18.4</v>
+      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO)</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P31" s="2" t="n"/>
@@ -2455,7 +2455,7 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E32" s="4" t="n">
@@ -2463,38 +2463,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>A Master EPI</t>
+          <t>Goiás Ferramentas</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>16.603.654/0001-40</t>
+          <t>09.497.806/0001-01</t>
         </is>
       </c>
       <c r="H32" s="5" t="inlineStr">
         <is>
-          <t>https://www.amasterepi.com.br/21946/luva-de-latex-neoprene-bicolor-std-volk-p</t>
+          <t>https://www.goiasferramentas.com.br/produto/13963-luva-de-latex-neoprene-kalipso-neoprex-azul-e-amarela-xg</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t>Luva de Latex Neoprene Bicolor Std Volk</t>
+          <t>Luva de Latex / Neoprene Kalipso Neoprex Azul e Amarela XG</t>
         </is>
       </c>
       <c r="J32" s="6" t="n">
-        <v>10.5</v>
+        <v>10.88</v>
       </c>
       <c r="K32" s="2" t="n"/>
       <c r="L32" s="2" t="n"/>
       <c r="M32" s="6" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="N32" s="6" t="n">
-        <v>32.85</v>
-      </c>
+        <v>10.88</v>
+      </c>
+      <c r="N32" s="2" t="n"/>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Entrega Econômica R$ 32,85 De 6 A 7 dia(s) Úteis</t>
+          <t>Frete não calculado (GO para GO)</t>
         </is>
       </c>
       <c r="P32" s="2" t="n"/>
@@ -2507,56 +2505,56 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>1112</t>
+          <t>1111</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t>LUVA DE ALGODÃO PIGMENTADA - PARA ATIVIDADES DE APOIO/MANUSEIO.</t>
+          <t>LUVA DE NEOPRENE - TAMANHOS VARIADOS; PARA MANIPULAÇÃO COMPATÍVEL DE PRODUTOS QUÍMICOS.</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>PR</t>
         </is>
       </c>
       <c r="E33" s="4" t="n">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>SEGURANCA TOTAL EPIS LTDA</t>
+          <t>A Master EPI</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>39.268.527/0001-37</t>
+          <t>16.603.654/0001-40</t>
         </is>
       </c>
       <c r="H33" s="5" t="inlineStr">
         <is>
-          <t>https://www.segurancatotal.com.br/produto/luva-tricotada-pigmentada-preta-handex-4-fios.html</t>
+          <t>https://www.amasterepi.com.br/21946/luva-de-latex-neoprene-bicolor-std-volk-p</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>Luva Tricotada Pigmentada Preta Handex 4 Fios</t>
+          <t>Luva de Latex Neoprene Bicolor Std Volk</t>
         </is>
       </c>
       <c r="J33" s="6" t="n">
-        <v>3.09</v>
+        <v>10.5</v>
       </c>
       <c r="K33" s="2" t="n"/>
       <c r="L33" s="2" t="n"/>
       <c r="M33" s="6" t="n">
-        <v>3.09</v>
+        <v>10.5</v>
       </c>
       <c r="N33" s="6" t="n">
-        <v>18.4</v>
+        <v>32.85</v>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
+          <t>Opção mais barata para o CEP 74933-130: Entrega Econômica R$ 32,85 De 6 A 7 dia(s) Úteis</t>
         </is>
       </c>
       <c r="P33" s="2" t="n"/>
@@ -2579,46 +2577,46 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E34" s="4" t="n">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>TR Distribuidora</t>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>14.213.841/0001-91</t>
+          <t>39.268.527/0001-37</t>
         </is>
       </c>
       <c r="H34" s="5" t="inlineStr">
         <is>
-          <t>https://www.trepis.com.br/luva-em-algodao-tricotada-modelo-cotton-black-sem-banho-e-com-pigmento-riscos-mecanicos-c-a-36347</t>
+          <t>https://www.segurancatotal.com.br/produto/luva-tricotada-pigmentada-preta-handex-4-fios.html</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>Luva de Algodão Tricotada Cotton Black Pigmentada para Riscos Mecânicos C.A. 36347</t>
+          <t>Luva Tricotada Pigmentada Preta Handex 4 Fios</t>
         </is>
       </c>
       <c r="J34" s="6" t="n">
-        <v>2.82</v>
+        <v>3.09</v>
       </c>
       <c r="K34" s="2" t="n"/>
       <c r="L34" s="2" t="n"/>
       <c r="M34" s="6" t="n">
-        <v>2.82</v>
+        <v>3.09</v>
       </c>
       <c r="N34" s="6" t="n">
-        <v>21.55</v>
+        <v>18.4</v>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: JADLOG .Package R$ 21,55 Capital de todo Brasil: 01 a 03 dias. Interior de Todo Brasil: 02 a 05 dias.</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P34" s="2" t="n"/>
@@ -2641,48 +2639,46 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>14/10/2026</t>
-        </is>
+          <t>PR</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>46304</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
+          <t>TR Distribuidora</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>31.893.116/0001-20</t>
+          <t>14.213.841/0001-91</t>
         </is>
       </c>
       <c r="H35" s="5" t="inlineStr">
         <is>
-          <t>https://www.loja.bhzepi.com.br/luva-de-segurana-malha-tricotada-pigmentada-branca</t>
+          <t>https://www.trepis.com.br/luva-em-algodao-tricotada-modelo-cotton-black-sem-banho-e-com-pigmento-riscos-mecanicos-c-a-36347</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t>Luva De Segurança Malha Tricotada Pigmentada branca</t>
+          <t>Luva de Algodão Tricotada Cotton Black Pigmentada para Riscos Mecânicos C.A. 36347</t>
         </is>
       </c>
       <c r="J35" s="6" t="n">
-        <v>3.9</v>
+        <v>2.82</v>
       </c>
       <c r="K35" s="2" t="n"/>
       <c r="L35" s="2" t="n"/>
       <c r="M35" s="6" t="n">
-        <v>3.9</v>
+        <v>2.82</v>
       </c>
       <c r="N35" s="6" t="n">
-        <v>20.62</v>
+        <v>21.55</v>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC</t>
+          <t>Opção mais barata para o CEP 74933-130: JADLOG .Package R$ 21,55 Capital de todo Brasil: 01 a 03 dias. Interior de Todo Brasil: 02 a 05 dias.</t>
         </is>
       </c>
       <c r="P35" s="2" t="n"/>
@@ -2705,46 +2701,48 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>46308</v>
+          <t>MG</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>14/10/2026</t>
+        </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>Dimensional Brasil Solucoes Ltda</t>
+          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>06.913.480/0001-68</t>
+          <t>31.893.116/0001-20</t>
         </is>
       </c>
       <c r="H36" s="5" t="inlineStr">
         <is>
-          <t>https://www.dimensional.com.br/luva-algodaopoliester-preta-pigmentada-tamanho-9-tatex-021123-kalipso/p</t>
+          <t>https://www.loja.bhzepi.com.br/luva-de-segurana-malha-tricotada-pigmentada-branca</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t>Luva Algodao/Poliester Preta Pigmentada Tatex 02.11.2.3 Tamanho 9 Kalipso</t>
+          <t>Luva De Segurança Malha Tricotada Pigmentada branca</t>
         </is>
       </c>
       <c r="J36" s="6" t="n">
-        <v>2.09</v>
+        <v>3.9</v>
       </c>
       <c r="K36" s="2" t="n"/>
       <c r="L36" s="2" t="n"/>
       <c r="M36" s="6" t="n">
-        <v>2.09</v>
+        <v>3.9</v>
       </c>
       <c r="N36" s="6" t="n">
-        <v>52.84</v>
+        <v>20.62</v>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Transportadora Em até 6 dias úteis R$ 52,84</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC</t>
         </is>
       </c>
       <c r="P36" s="2" t="n"/>
@@ -2757,17 +2755,17 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>1113</t>
+          <t>1112</t>
         </is>
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t>ÓCULOS DE PROTEÇÃO INCOLOR - PARA MANIPULAÇÃO E APLICAÇÃO DE PRODUTOS QUÍMICOS.</t>
+          <t>LUVA DE ALGODÃO PIGMENTADA - PARA ATIVIDADES DE APOIO/MANUSEIO.</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>MG</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E37" s="4" t="n">
@@ -2775,38 +2773,38 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
+          <t>Dimensional Brasil Solucoes Ltda</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>31.893.116/0001-20</t>
+          <t>06.913.480/0001-68</t>
         </is>
       </c>
       <c r="H37" s="5" t="inlineStr">
         <is>
-          <t>https://www.loja.bhzepi.com.br/produto/oculos-de-seguranca-roma-incolor-protecao-uv-antirrisco</t>
+          <t>https://www.dimensional.com.br/luva-algodaopoliester-preta-pigmentada-tamanho-9-tatex-021123-kalipso/p</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>Oculos De Segurança Roma Incolor Proteção Uv Antirrisco</t>
+          <t>Luva Algodao/Poliester Preta Pigmentada Tatex 02.11.2.3 Tamanho 9 Kalipso</t>
         </is>
       </c>
       <c r="J37" s="6" t="n">
-        <v>70</v>
+        <v>2.09</v>
       </c>
       <c r="K37" s="2" t="n"/>
       <c r="L37" s="2" t="n"/>
       <c r="M37" s="6" t="n">
-        <v>70</v>
+        <v>2.09</v>
       </c>
       <c r="N37" s="6" t="n">
-        <v>20.62</v>
+        <v>52.84</v>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC R$ 26,55 5 dias úteis Jadlog Package R$ 40,39 3 dias úteis SEDEX</t>
+          <t>Opção mais barata para o CEP 74933-130: Transportadora Em até 6 dias úteis R$ 52,84</t>
         </is>
       </c>
       <c r="P37" s="2" t="n"/>
@@ -2829,7 +2827,7 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
+          <t>MG</t>
         </is>
       </c>
       <c r="E38" s="4" t="n">
@@ -2837,38 +2835,38 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
+          <t>BHZ EPI DISTRIBUIDORA LTDA</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>27.061.442/0002-85</t>
+          <t>31.893.116/0001-20</t>
         </is>
       </c>
       <c r="H38" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojas360.com.br/oculos-de-seguranca-urano</t>
+          <t>https://www.loja.bhzepi.com.br/produto/oculos-de-seguranca-roma-incolor-protecao-uv-antirrisco</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t>Óculos de Segurança Urano Incolor Anti Risco | C.A. 42547</t>
+          <t>Oculos De Segurança Roma Incolor Proteção Uv Antirrisco</t>
         </is>
       </c>
       <c r="J38" s="6" t="n">
-        <v>9.41</v>
+        <v>70</v>
       </c>
       <c r="K38" s="2" t="n"/>
       <c r="L38" s="2" t="n"/>
       <c r="M38" s="6" t="n">
-        <v>9.41</v>
+        <v>70</v>
       </c>
       <c r="N38" s="6" t="n">
-        <v>18.4</v>
+        <v>20.62</v>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 20,62 7 dias úteis PAC R$ 26,55 5 dias úteis Jadlog Package R$ 40,39 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P38" s="2" t="n"/>
@@ -2899,38 +2897,38 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>SEGURANCA TOTAL EPIS LTDA</t>
+          <t>LOJAS 360 INDUSTRIA, COMERCIO, IMPORTACAO, EXPORTACAO LTDA</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>39.268.527/0001-37</t>
+          <t>27.061.442/0002-85</t>
         </is>
       </c>
       <c r="H39" s="5" t="inlineStr">
         <is>
-          <t>https://www.segurancatotal.com.br/produto/oculos-de-protecao-sky-deltaplus-incolor.html</t>
+          <t>https://www.lojas360.com.br/oculos-de-seguranca-urano</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t>Óculos De Proteção Sky Deltaplus Incolor</t>
+          <t>Óculos de Segurança Urano Incolor Anti Risco | C.A. 42547</t>
         </is>
       </c>
       <c r="J39" s="6" t="n">
-        <v>3.99</v>
+        <v>9.41</v>
       </c>
       <c r="K39" s="2" t="n"/>
       <c r="L39" s="2" t="n"/>
       <c r="M39" s="6" t="n">
-        <v>3.99</v>
+        <v>9.41</v>
       </c>
       <c r="N39" s="6" t="n">
         <v>18.4</v>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
+          <t>Opção mais barata para o CEP 74933-130: SEDEX R$ 28,85 Até 6 dias úteis após o faturamento do pedido.rn PAC R$ 18,40 Até 10 dias úteis após o faturamento do pedido.rn Logística Própria FAVOR</t>
         </is>
       </c>
       <c r="P39" s="2" t="n"/>
@@ -2953,7 +2951,7 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>SP</t>
         </is>
       </c>
       <c r="E40" s="4" t="n">
@@ -2961,36 +2959,38 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>ZEUS DO BRASIL LTDA (loja EPI Zeus)</t>
+          <t>SEGURANCA TOTAL EPIS LTDA</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>82.699.588/0001-88</t>
+          <t>39.268.527/0001-37</t>
         </is>
       </c>
       <c r="H40" s="5" t="inlineStr">
         <is>
-          <t>https://www.epizeus.com.br/oculos-protec-o-lente-incolor-policarbonato-ca-28018</t>
+          <t>https://www.segurancatotal.com.br/produto/oculos-de-protecao-sky-deltaplus-incolor.html</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>Óculos proteção lente incolor policarbonato - CA 10346</t>
+          <t>Óculos De Proteção Sky Deltaplus Incolor</t>
         </is>
       </c>
       <c r="J40" s="6" t="n">
-        <v>15.9</v>
+        <v>3.99</v>
       </c>
       <c r="K40" s="2" t="n"/>
       <c r="L40" s="2" t="n"/>
       <c r="M40" s="6" t="n">
-        <v>15.9</v>
-      </c>
-      <c r="N40" s="2" t="n"/>
+        <v>3.99</v>
+      </c>
+      <c r="N40" s="6" t="n">
+        <v>18.4</v>
+      </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t>Frete grátis informado na página do produto: "🚚 FRETE GRÁTIS PARA TODO O BRASIL*" (sem calculadora de CEP no site)</t>
+          <t>Opção mais barata para o CEP 74933-130: R$ 18,40 7 dias úteis PAC R$ 28,85 3 dias úteis SEDEX</t>
         </is>
       </c>
       <c r="P40" s="2" t="n"/>
@@ -3013,48 +3013,44 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>SP</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr">
-        <is>
-          <t>14/10/2026</t>
-        </is>
+          <t>SC</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>46308</v>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>SINGULAR COMERCIO DE EQUIPAMENTOS DE PROTECAO INDIVIDUAL LTDA (Loja do EPI)</t>
+          <t>ZEUS DO BRASIL LTDA (loja EPI Zeus)</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>20.838.307/0001-73</t>
+          <t>82.699.588/0001-88</t>
         </is>
       </c>
       <c r="H41" s="5" t="inlineStr">
         <is>
-          <t>https://www.lojadoepi.com.br/oculos-de-protecao-vvision-600-incolor-antiembacante-volk-ca-42922-p3187</t>
+          <t>https://www.epizeus.com.br/oculos-protec-o-lente-incolor-policarbonato-ca-28018</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t>Óculos de Proteção Vvision 600 Incolor Antiembaçante Volk CA 42922</t>
+          <t>Óculos proteção lente incolor policarbonato - CA 10346</t>
         </is>
       </c>
       <c r="J41" s="6" t="n">
-        <v>26.93</v>
+        <v>15.9</v>
       </c>
       <c r="K41" s="2" t="n"/>
       <c r="L41" s="2" t="n"/>
       <c r="M41" s="6" t="n">
-        <v>26.93</v>
-      </c>
-      <c r="N41" s="6" t="n">
-        <v>21.39</v>
-      </c>
+        <v>15.9</v>
+      </c>
+      <c r="N41" s="2" t="n"/>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: Pac R$ 21,39 7 dia(s) útil(eis)</t>
+          <t>Frete grátis informado na página do produto: "🚚 FRETE GRÁTIS PARA TODO O BRASIL*" (sem calculadora de CEP no site)</t>
         </is>
       </c>
       <c r="P41" s="2" t="n"/>
@@ -3077,43 +3073,47 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>RS</t>
+          <t>GO</t>
         </is>
       </c>
       <c r="E42" s="4" t="n">
-        <v>46308</v>
+        <v>46304</v>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
+          <t>Casa do Pica-Pau</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>46.412.993/0001-00</t>
-        </is>
-      </c>
-      <c r="H42" s="2" t="n"/>
+          <t>50.223.823/0001-54</t>
+        </is>
+      </c>
+      <c r="H42" s="5" t="inlineStr">
+        <is>
+          <t>https://www.casadopicapau.com.br/oculos-de-protecao-stihl-policarbonato-incolor/p?skuId=5055</t>
+        </is>
+      </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t>ÓCULOS SEGURANCA DISMA II INCOLOR</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="n"/>
+          <t>Óculos de Proteção STIHL em Policarbonato Incolor</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="n">
+        <v>16.1</v>
+      </c>
       <c r="K42" s="2" t="n"/>
       <c r="L42" s="2" t="n"/>
-      <c r="M42" s="2" t="n"/>
+      <c r="M42" s="6" t="n">
+        <v>16.1</v>
+      </c>
       <c r="N42" s="2" t="n"/>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t>Preço não exibido (motivo não identificado)</t>
-        </is>
-      </c>
-      <c r="P42" s="5" t="inlineStr">
-        <is>
-          <t>https://www.supriflex.com.br/produto/oculos-seguranca-disma-ii-incolor.html</t>
-        </is>
-      </c>
+          <t>Frete não calculado (GO para GO)</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -3123,17 +3123,17 @@
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1113</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t>MÁSCARA DE PROTEÇÃO DESCARTÁVEL - USO CONFORME RISCO/ATIVIDADE.</t>
+          <t>ÓCULOS DE PROTEÇÃO INCOLOR - PARA MANIPULAÇÃO E APLICAÇÃO DE PRODUTOS QUÍMICOS.</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
+          <t>RS</t>
         </is>
       </c>
       <c r="E43" s="4" t="n">
@@ -3141,39 +3141,35 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>ZEUS DO BRASIL LTDA (loja EPI Zeus)</t>
+          <t>SUPRIFLEX SUPRIMENTOS ONLINE LTDA</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>82.699.588/0001-88</t>
-        </is>
-      </c>
-      <c r="H43" s="5" t="inlineStr">
-        <is>
-          <t>https://www.epizeus.com.br/mascara-de-protec-o-pff1-sem-valvula-delta-plus-ca-38502</t>
-        </is>
-      </c>
+          <t>46.412.993/0001-00</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="n"/>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t>Máscara de Proteção PFF1 - Sem Válvula - CA 45020</t>
-        </is>
-      </c>
-      <c r="J43" s="6" t="n">
-        <v>1.9</v>
-      </c>
+          <t>ÓCULOS SEGURANCA DISMA II INCOLOR</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="n"/>
       <c r="K43" s="2" t="n"/>
       <c r="L43" s="2" t="n"/>
-      <c r="M43" s="6" t="n">
-        <v>1.9</v>
-      </c>
+      <c r="M43" s="2" t="n"/>
       <c r="N43" s="2" t="n"/>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t>Frete grátis informado na página do produto: "🚚 FRETE GRÁTIS PARA TODO O BRASIL*" (sem calculadora de CEP no site)</t>
-        </is>
-      </c>
-      <c r="P43" s="2" t="n"/>
+          <t>Preço não exibido (motivo não identificado)</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="inlineStr">
+        <is>
+          <t>https://www.supriflex.com.br/produto/oculos-seguranca-disma-ii-incolor.html</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -3193,30 +3189,30 @@
       </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>GO</t>
+          <t>SC</t>
         </is>
       </c>
       <c r="E44" s="4" t="n">
-        <v>46307</v>
+        <v>46308</v>
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>Goiás Ferramentas</t>
+          <t>ZEUS DO BRASIL LTDA (loja EPI Zeus)</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>09.497.806/0001-01</t>
+          <t>82.699.588/0001-88</t>
         </is>
       </c>
       <c r="H44" s="5" t="inlineStr">
         <is>
-          <t>https://www.goiasferramentas.com.br/produto/10985-mascara-descartavel-pff2-com-valvula</t>
+          <t>https://www.epizeus.com.br/mascara-de-protec-o-pff1-sem-valvula-delta-plus-ca-38502</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t>MASCARA DESCARTAVEL PFF2 COM VALVULA</t>
+          <t>Máscara de Proteção PFF1 - Sem Válvula - CA 45020</t>
         </is>
       </c>
       <c r="J44" s="6" t="n">
@@ -3230,7 +3226,7 @@
       <c r="N44" s="2" t="n"/>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t>Frete não calculado (GO para GO)</t>
+          <t>Frete grátis informado na página do produto: "🚚 FRETE GRÁTIS PARA TODO O BRASIL*" (sem calculadora de CEP no site)</t>
         </is>
       </c>
       <c r="P44" s="2" t="n"/>
@@ -3257,39 +3253,35 @@
         </is>
       </c>
       <c r="E45" s="4" t="n">
-        <v>46307</v>
+        <v>46311</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>Fermarcs Ferramentas</t>
+          <t>Mais Segurança EPI</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>08.615.223/0001-75</t>
+          <t>43.903.641/0001-69</t>
         </is>
       </c>
       <c r="H45" s="5" t="inlineStr">
         <is>
-          <t>https://www.fermarcsferramentas.com.br/epi-e-epc/respiratoria/mascara-de-protecao-msk95-pff-2-n95</t>
+          <t>https://maisseguranca.online/#/produto-detalhes/nUNEWOBUivWtuxf5g7uS3ulpNCn2/-NWsT-o_-VgTH2z0Xn2v</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>Mascara De Protecao Msk95 Pff-2 N95</t>
+          <t>RESPIRADOR PFF2 AZ S/VALV PRO SAFETY - DELTA PLUS CA.38504</t>
         </is>
       </c>
       <c r="J45" s="6" t="n">
-        <v>2.99</v>
+        <v>1</v>
       </c>
       <c r="K45" s="2" t="n"/>
-      <c r="L45" s="2" t="inlineStr">
-        <is>
-          <t>Característica não confirmada na página do produto: descartável.</t>
-        </is>
-      </c>
+      <c r="L45" s="2" t="n"/>
       <c r="M45" s="6" t="n">
-        <v>2.99</v>
+        <v>1</v>
       </c>
       <c r="N45" s="2" t="n"/>
       <c r="O45" s="3" t="inlineStr">
@@ -3317,48 +3309,44 @@
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>PR</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="inlineStr">
-        <is>
-          <t>14/10/2026</t>
-        </is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="E46" s="4" t="n">
+        <v>46307</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>TR Distribuidora de Equipamentos de Segurança LTDA</t>
+          <t>Goiás Ferramentas</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>14.213.841/0001-91</t>
+          <t>09.497.806/0001-01</t>
         </is>
       </c>
       <c r="H46" s="5" t="inlineStr">
         <is>
-          <t>https://www.trepis.com.br/mascara-descartavel-confec-em-tnt-tripla-branca-com-elastico-pct-c50un</t>
+          <t>https://www.goiasferramentas.com.br/produto/10985-mascara-descartavel-pff2-com-valvula</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t>Máscara Descartável Tripla TNT Branca com Elástico Pacote com 50 Unidades</t>
+          <t>MASCARA DESCARTAVEL PFF2 COM VALVULA</t>
         </is>
       </c>
       <c r="J46" s="6" t="n">
-        <v>10.81</v>
+        <v>1.9</v>
       </c>
       <c r="K46" s="2" t="n"/>
       <c r="L46" s="2" t="n"/>
       <c r="M46" s="6" t="n">
-        <v>10.81</v>
-      </c>
-      <c r="N46" s="6" t="n">
-        <v>21.55</v>
-      </c>
+        <v>1.9</v>
+      </c>
+      <c r="N46" s="2" t="n"/>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: JADLOG .Package R$ 21,55 Capital de todo Brasil: 01 a 03 dias. Interior de Todo Brasil: 02 a 05 dias.</t>
+          <t>Frete não calculado (GO para GO)</t>
         </is>
       </c>
       <c r="P46" s="2" t="n"/>
@@ -3381,48 +3369,48 @@
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>SC</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="inlineStr">
-        <is>
-          <t>14/10/2026</t>
-        </is>
+          <t>GO</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="n">
+        <v>46307</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>ASTRO DISTRIBUIDORA LTDA</t>
+          <t>Fermarcs Ferramentas</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>18.597.685/0001-60</t>
+          <t>08.615.223/0001-75</t>
         </is>
       </c>
       <c r="H47" s="5" t="inlineStr">
         <is>
-          <t>https://www.astrodistribuidora.com/mascara-de-tnt-descartavel-com-elastico-volk</t>
+          <t>https://www.fermarcsferramentas.com.br/epi-e-epc/respiratoria/mascara-de-protecao-msk95-pff-2-n95</t>
         </is>
       </c>
       <c r="I47" s="3" t="inlineStr">
         <is>
-          <t>Máscara de TNT Descartável com Elástico - Volk (100 Unidades)</t>
+          <t>Mascara De Protecao Msk95 Pff-2 N95</t>
         </is>
       </c>
       <c r="J47" s="6" t="n">
-        <v>10.42</v>
+        <v>2.99</v>
       </c>
       <c r="K47" s="2" t="n"/>
-      <c r="L47" s="2" t="n"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>Característica não confirmada na página do produto: descartável.</t>
+        </is>
+      </c>
       <c r="M47" s="6" t="n">
-        <v>10.42</v>
-      </c>
-      <c r="N47" s="6" t="n">
-        <v>26.82</v>
-      </c>
+        <v>2.99</v>
+      </c>
+      <c r="N47" s="2" t="n"/>
       <c r="O47" s="3" t="inlineStr">
         <is>
-          <t>Opção mais barata para o CEP 74933-130: JADLOG - Entrega em até 5 dias úteis - R$26,82 BRASPRESS - Entrega em até 15 dias úteis -</t>
+          <t>Frete não calculado (GO para GO)</t>
         </is>
       </c>
       <c r="P47" s="2" t="n"/>
@@ -5251,8 +5239,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId10"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H12" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId13"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H17" r:id="rId16"/>
@@ -5280,8 +5268,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H39" r:id="rId38"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H40" r:id="rId39"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H41" r:id="rId40"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P42" r:id="rId41"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P43" r:id="rId42"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H44" r:id="rId43"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H45" r:id="rId44"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="H46" r:id="rId45"/>
